--- a/static/downloads/Input Template -- File name will be analysis title.xlsx
+++ b/static/downloads/Input Template -- File name will be analysis title.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeamLorenzen\Documents\App0\static\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{E9F465D6-340A-49B4-AB73-DD4914998482}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B1A27305-03F2-47EF-B15D-8A1C80CDDA98}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="6852" windowHeight="4692" xr2:uid="{A1AE285A-40C5-42A2-B68C-1B9EC99F826A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="27">
   <si>
     <t>gid</t>
   </si>
@@ -97,6 +97,15 @@
   </si>
   <si>
     <t>expected sign</t>
+  </si>
+  <si>
+    <t>log y</t>
+  </si>
+  <si>
+    <t>mean log y</t>
+  </si>
+  <si>
+    <t>log y -mean log y</t>
   </si>
 </sst>
 </file>
@@ -448,13 +457,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE90F50-471E-417F-9EB4-10FF26C6D164}">
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:N212"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="23.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -480,7 +489,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -503,7 +512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -517,7 +526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -527,8 +536,17 @@
       <c r="G4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -539,7 +557,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <f>EXP(2-1.2*(LN(F5)-LN(AVERAGE(F:F)))+0.02*H5)</f>
+        <f t="shared" ref="E5:E36" si="0">EXP(2-1.2*(LN(F5)-LN(AVERAGE(F:F)))+0.02*H5)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F5">
@@ -552,8 +570,20 @@
         <f>G5</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5">
+        <f>LN(E5)</f>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE($L$5:$L$108)</f>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N5">
+        <f>L5-M5</f>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -564,7 +594,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <f>EXP(2-1.2*(LN(F6)-LN(AVERAGE(F:F)))+0.02*H6)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F6">
@@ -577,8 +607,20 @@
         <f>IF(H5*0.5&gt;1,G6+H5*0.5,G6)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6">
+        <f t="shared" ref="L6:L69" si="1">LN(E6)</f>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M6">
+        <f t="shared" ref="M6:M69" si="2">AVERAGE($L$5:$L$108)</f>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N6">
+        <f t="shared" ref="N6:N69" si="3">L6-M6</f>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -589,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <f>EXP(2-1.2*(LN(F7)-LN(AVERAGE(F:F)))+0.02*H7)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F7">
@@ -599,11 +641,23 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <f t="shared" ref="H7:H70" si="0">IF(H6*0.5&gt;1,G7+H6*0.5,G7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" ref="H7:H70" si="4">IF(H6*0.5&gt;1,G7+H6*0.5,G7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -614,7 +668,7 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <f>EXP(2-1.2*(LN(F8)-LN(AVERAGE(F:F)))+0.02*H8)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F8">
@@ -624,11 +678,23 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -639,7 +705,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <f>EXP(2-1.2*(LN(F9)-LN(AVERAGE(F:F)))+0.02*H9)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F9">
@@ -649,22 +715,34 @@
         <v>0</v>
       </c>
       <c r="H9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <f>EXP(2-1.2*(LN(F10)-LN(AVERAGE(F:F)))+0.02*H10)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F10">
@@ -674,22 +752,34 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>7</v>
-      </c>
-      <c r="E11">
-        <f>EXP(2-1.2*(LN(F11)-LN(AVERAGE(F:F)))+0.02*H11)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F11">
@@ -699,22 +789,34 @@
         <v>0</v>
       </c>
       <c r="H11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <f>EXP(2-1.2*(LN(F12)-LN(AVERAGE(F:F)))+0.02*H12)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F12">
@@ -724,11 +826,23 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>6</v>
       </c>
@@ -739,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <f>EXP(2-1.2*(LN(F13)-LN(AVERAGE(F:F)))+0.02*H13)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F13">
@@ -749,11 +863,23 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>6</v>
       </c>
@@ -764,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <f>EXP(2-1.2*(LN(F14)-LN(AVERAGE(F:F)))+0.02*H14)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F14">
@@ -774,11 +900,23 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
         <v>6</v>
       </c>
@@ -789,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="E15">
-        <f>EXP(2-1.2*(LN(F15)-LN(AVERAGE(F:F)))+0.02*H15)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F15">
@@ -799,11 +937,23 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>6</v>
       </c>
@@ -814,7 +964,7 @@
         <v>12</v>
       </c>
       <c r="E16">
-        <f>EXP(2-1.2*(LN(F16)-LN(AVERAGE(F:F)))+0.02*H16)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F16">
@@ -824,11 +974,23 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
         <v>6</v>
       </c>
@@ -839,7 +1001,7 @@
         <v>13</v>
       </c>
       <c r="E17">
-        <f>EXP(2-1.2*(LN(F17)-LN(AVERAGE(F:F)))+0.02*H17)</f>
+        <f t="shared" si="0"/>
         <v>10.240192912859774</v>
       </c>
       <c r="F17">
@@ -849,11 +1011,23 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>-0.76869467340092967</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>6</v>
       </c>
@@ -864,7 +1038,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <f>EXP(2-1.2*(LN(F18)-LN(AVERAGE(F:F)))+0.02*H18)</f>
+        <f t="shared" si="0"/>
         <v>75.665359896992911</v>
       </c>
       <c r="F18">
@@ -874,22 +1048,34 @@
         <v>100</v>
       </c>
       <c r="H18">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>4.3263204585803692</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>1.2313053265990699</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <f>EXP(2-1.2*(LN(F19)-LN(AVERAGE(F:F)))+0.02*H19)</f>
         <v>205.67977285180959</v>
       </c>
       <c r="F19">
@@ -899,11 +1085,23 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>5.3263204585803692</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>2.2313053265990699</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>6</v>
       </c>
@@ -914,7 +1112,7 @@
         <v>16</v>
       </c>
       <c r="E20">
-        <f>EXP(2-1.2*(LN(F20)-LN(AVERAGE(F:F)))+0.02*H20)</f>
+        <f t="shared" si="0"/>
         <v>339.10861645354925</v>
       </c>
       <c r="F20">
@@ -924,11 +1122,23 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>5.8263204585803692</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>2.7313053265990699</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
         <v>6</v>
       </c>
@@ -939,7 +1149,7 @@
         <v>17</v>
       </c>
       <c r="E21">
-        <f>EXP(2-1.2*(LN(F21)-LN(AVERAGE(F:F)))+0.02*H21)</f>
+        <f t="shared" si="0"/>
         <v>58.928241539157753</v>
       </c>
       <c r="F21">
@@ -949,11 +1159,23 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>87.5</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>4.0763204585803692</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>0.98130532659906988</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>6</v>
       </c>
@@ -964,7 +1186,7 @@
         <v>18</v>
       </c>
       <c r="E22">
-        <f>EXP(2-1.2*(LN(F22)-LN(AVERAGE(F:F)))+0.02*H22)</f>
+        <f t="shared" si="0"/>
         <v>24.564945784116286</v>
       </c>
       <c r="F22">
@@ -974,11 +1196,23 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>43.75</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>3.2013204585803696</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>0.10630532659907033</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
         <v>6</v>
       </c>
@@ -989,7 +1223,7 @@
         <v>19</v>
       </c>
       <c r="E23">
-        <f>EXP(2-1.2*(LN(F23)-LN(AVERAGE(F:F)))+0.02*H23)</f>
+        <f t="shared" si="0"/>
         <v>117.19280196551868</v>
       </c>
       <c r="F23">
@@ -999,11 +1233,23 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>121.875</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>4.7638204585803692</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>1.6688053265990699</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>6</v>
       </c>
@@ -1014,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <f>EXP(2-1.2*(LN(F24)-LN(AVERAGE(F:F)))+0.02*H24)</f>
+        <f t="shared" si="0"/>
         <v>255.97261307484004</v>
       </c>
       <c r="F24">
@@ -1024,11 +1270,23 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>160.9375</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>5.5450704585803692</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="3"/>
+        <v>2.4500553265990699</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>6</v>
       </c>
@@ -1039,7 +1297,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <f>EXP(2-1.2*(LN(F25)-LN(AVERAGE(F:F)))+0.02*H25)</f>
+        <f t="shared" si="0"/>
         <v>378.30299877381174</v>
       </c>
       <c r="F25">
@@ -1049,11 +1307,23 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>180.46875</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>5.9356954585803692</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>2.8406803265990699</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
         <v>6</v>
       </c>
@@ -1064,7 +1334,7 @@
         <v>22</v>
       </c>
       <c r="E26">
-        <f>EXP(2-1.2*(LN(F26)-LN(AVERAGE(F:F)))+0.02*H26)</f>
+        <f t="shared" si="0"/>
         <v>62.240627302086097</v>
       </c>
       <c r="F26">
@@ -1074,11 +1344,23 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>90.234375</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>4.1310079585803692</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="3"/>
+        <v>1.0359928265990699</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>6</v>
       </c>
@@ -1089,7 +1371,7 @@
         <v>23</v>
       </c>
       <c r="E27">
-        <f>EXP(2-1.2*(LN(F27)-LN(AVERAGE(F:F)))+0.02*H27)</f>
+        <f t="shared" si="0"/>
         <v>25.245911165786211</v>
       </c>
       <c r="F27">
@@ -1099,11 +1381,23 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>45.1171875</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>3.2286642085803696</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>0.13364907659907033</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>6</v>
       </c>
@@ -1114,7 +1408,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <f>EXP(2-1.2*(LN(F28)-LN(AVERAGE(F:F)))+0.02*H28)</f>
+        <f t="shared" si="0"/>
         <v>118.8060502402947</v>
       </c>
       <c r="F28">
@@ -1124,11 +1418,23 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>122.55859375</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>4.7774923335803692</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="3"/>
+        <v>1.6824772015990699</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>6</v>
       </c>
@@ -1139,7 +1445,7 @@
         <v>25</v>
       </c>
       <c r="E29">
-        <f>EXP(2-1.2*(LN(F29)-LN(AVERAGE(F:F)))+0.02*H29)</f>
+        <f t="shared" si="0"/>
         <v>257.72842031640727</v>
       </c>
       <c r="F29">
@@ -1149,11 +1455,23 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>161.279296875</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>5.5519063960803692</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="3"/>
+        <v>2.4568912640990699</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>6</v>
       </c>
@@ -1164,7 +1482,7 @@
         <v>26</v>
       </c>
       <c r="E30">
-        <f>EXP(2-1.2*(LN(F30)-LN(AVERAGE(F:F)))+0.02*H30)</f>
+        <f t="shared" si="0"/>
         <v>379.59823888579405</v>
       </c>
       <c r="F30">
@@ -1174,11 +1492,23 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>180.6396484375</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>5.9391134273303692</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="3"/>
+        <v>2.8440982953490699</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>6</v>
       </c>
@@ -1189,7 +1519,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <f>EXP(2-1.2*(LN(F31)-LN(AVERAGE(F:F)))+0.02*H31)</f>
+        <f t="shared" si="0"/>
         <v>62.347086504281485</v>
       </c>
       <c r="F31">
@@ -1199,11 +1529,23 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>90.31982421875</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>4.1327169429553692</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="3"/>
+        <v>1.0377018109740699</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>6</v>
       </c>
@@ -1214,7 +1556,7 @@
         <v>28</v>
       </c>
       <c r="E32">
-        <f>EXP(2-1.2*(LN(F32)-LN(AVERAGE(F:F)))+0.02*H32)</f>
+        <f t="shared" si="0"/>
         <v>25.267492819007565</v>
       </c>
       <c r="F32">
@@ -1224,11 +1566,23 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>45.159912109375</v>
       </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>3.2295187007678696</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="3"/>
+        <v>0.13450356878657033</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>6</v>
       </c>
@@ -1239,7 +1593,7 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <f>EXP(2-1.2*(LN(F33)-LN(AVERAGE(F:F)))+0.02*H33)</f>
+        <f t="shared" si="0"/>
         <v>118.85682050610031</v>
       </c>
       <c r="F33">
@@ -1249,11 +1603,23 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>122.5799560546875</v>
       </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>4.7779195796741192</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="3"/>
+        <v>1.6829044476928199</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>6</v>
       </c>
@@ -1264,7 +1630,7 @@
         <v>30</v>
       </c>
       <c r="E34">
-        <f>EXP(2-1.2*(LN(F34)-LN(AVERAGE(F:F)))+0.02*H34)</f>
+        <f t="shared" si="0"/>
         <v>257.78348292793356</v>
       </c>
       <c r="F34">
@@ -1274,11 +1640,23 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>161.28997802734375</v>
       </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>5.5521200191272442</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="3"/>
+        <v>2.4571048871459449</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>6</v>
       </c>
@@ -1289,7 +1667,7 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <f>EXP(2-1.2*(LN(F35)-LN(AVERAGE(F:F)))+0.02*H35)</f>
+        <f t="shared" si="0"/>
         <v>233.37861903535872</v>
       </c>
       <c r="F35">
@@ -1299,11 +1677,23 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>180.64498901367188</v>
       </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>5.4526621091240104</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="3"/>
+        <v>2.3576469771427111</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>6</v>
       </c>
@@ -1314,7 +1704,7 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <f>EXP(2-1.2*(LN(F36)-LN(AVERAGE(F:F)))+0.02*H36)</f>
+        <f t="shared" si="0"/>
         <v>38.329208094850323</v>
       </c>
       <c r="F36">
@@ -1324,11 +1714,23 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>90.322494506835938</v>
       </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36">
+        <f t="shared" si="1"/>
+        <v>3.6462122189872916</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="3"/>
+        <v>0.55119708700599235</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>6</v>
       </c>
@@ -1339,7 +1741,7 @@
         <v>33</v>
       </c>
       <c r="E37">
-        <f>EXP(2-1.2*(LN(F37)-LN(AVERAGE(F:F)))+0.02*H37)</f>
+        <f t="shared" ref="E37:E68" si="5">EXP(2-1.2*(LN(F37)-LN(AVERAGE(F:F)))+0.02*H37)</f>
         <v>15.533318133281966</v>
       </c>
       <c r="F37">
@@ -1349,11 +1751,23 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>45.161247253417969</v>
       </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>2.7429872739189323</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="3"/>
+        <v>-0.35202785806236703</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
         <v>6</v>
       </c>
@@ -1364,7 +1778,7 @@
         <v>34</v>
       </c>
       <c r="E38">
-        <f>EXP(2-1.2*(LN(F38)-LN(AVERAGE(F:F)))+0.02*H38)</f>
+        <f t="shared" si="5"/>
         <v>73.066851889367172</v>
       </c>
       <c r="F38">
@@ -1374,11 +1788,23 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>122.58062362670898</v>
       </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L38">
+        <f t="shared" si="1"/>
+        <v>4.2913748013847526</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="3"/>
+        <v>1.1963596694034533</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
         <v>6</v>
       </c>
@@ -1389,7 +1815,7 @@
         <v>35</v>
       </c>
       <c r="E39">
-        <f>EXP(2-1.2*(LN(F39)-LN(AVERAGE(F:F)))+0.02*H39)</f>
+        <f t="shared" si="5"/>
         <v>158.47051727274626</v>
       </c>
       <c r="F39">
@@ -1399,11 +1825,23 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>161.29031181335449</v>
       </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L39">
+        <f t="shared" si="1"/>
+        <v>5.0655685651176627</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="3"/>
+        <v>1.9705534331363634</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
         <v>6</v>
       </c>
@@ -1414,7 +1852,7 @@
         <v>36</v>
       </c>
       <c r="E40">
-        <f>EXP(2-1.2*(LN(F40)-LN(AVERAGE(F:F)))+0.02*H40)</f>
+        <f t="shared" si="5"/>
         <v>233.37939802184118</v>
       </c>
       <c r="F40">
@@ -1424,11 +1862,23 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>180.64515590667725</v>
       </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L40">
+        <f t="shared" si="1"/>
+        <v>5.4526654469841178</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="3"/>
+        <v>2.3576503150028185</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
         <v>6</v>
       </c>
@@ -1439,7 +1889,7 @@
         <v>37</v>
       </c>
       <c r="E41">
-        <f>EXP(2-1.2*(LN(F41)-LN(AVERAGE(F:F)))+0.02*H41)</f>
+        <f t="shared" si="5"/>
         <v>38.329272063671027</v>
       </c>
       <c r="F41">
@@ -1449,11 +1899,23 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>90.322577953338623</v>
       </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L41">
+        <f t="shared" si="1"/>
+        <v>3.6462138879173454</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="3"/>
+        <v>0.55119875593604606</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
         <v>6</v>
       </c>
@@ -1464,7 +1926,7 @@
         <v>38</v>
       </c>
       <c r="E42">
-        <f>EXP(2-1.2*(LN(F42)-LN(AVERAGE(F:F)))+0.02*H42)</f>
+        <f t="shared" si="5"/>
         <v>15.533331095298108</v>
       </c>
       <c r="F42">
@@ -1474,11 +1936,23 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>45.161288976669312</v>
       </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42">
+        <f t="shared" si="1"/>
+        <v>2.7429881083839591</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="3"/>
+        <v>-0.35202702359734017</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" t="s">
         <v>6</v>
       </c>
@@ -1489,7 +1963,7 @@
         <v>39</v>
       </c>
       <c r="E43">
-        <f>EXP(2-1.2*(LN(F43)-LN(AVERAGE(F:F)))+0.02*H43)</f>
+        <f t="shared" si="5"/>
         <v>73.066882375239786</v>
       </c>
       <c r="F43">
@@ -1499,11 +1973,23 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>122.58064448833466</v>
       </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L43">
+        <f t="shared" si="1"/>
+        <v>4.291375218617266</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="3"/>
+        <v>1.1963600866359667</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
         <v>6</v>
       </c>
@@ -1514,7 +2000,7 @@
         <v>40</v>
       </c>
       <c r="E44">
-        <f>EXP(2-1.2*(LN(F44)-LN(AVERAGE(F:F)))+0.02*H44)</f>
+        <f t="shared" si="5"/>
         <v>21.446656813880434</v>
       </c>
       <c r="F44">
@@ -1524,11 +2010,23 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>61.290322244167328</v>
       </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L44">
+        <f t="shared" si="1"/>
+        <v>3.0655687737339194</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="3"/>
+        <v>-2.9446358247379845E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
         <v>6</v>
       </c>
@@ -1539,7 +2037,7 @@
         <v>41</v>
       </c>
       <c r="E45">
-        <f>EXP(2-1.2*(LN(F45)-LN(AVERAGE(F:F)))+0.02*H45)</f>
+        <f t="shared" si="5"/>
         <v>11.619277256949339</v>
       </c>
       <c r="F45">
@@ -1549,11 +2047,23 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>30.645161122083664</v>
       </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L45">
+        <f t="shared" si="1"/>
+        <v>2.4526655512922462</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="3"/>
+        <v>-0.64234958068905312</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="s">
         <v>6</v>
       </c>
@@ -1564,7 +2074,7 @@
         <v>42</v>
       </c>
       <c r="E46">
-        <f>EXP(2-1.2*(LN(F46)-LN(AVERAGE(F:F)))+0.02*H46)</f>
+        <f t="shared" si="5"/>
         <v>8.5524170599829503</v>
       </c>
       <c r="F46">
@@ -1574,11 +2084,23 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>15.322580561041832</v>
       </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L46">
+        <f t="shared" si="1"/>
+        <v>2.1462139400714095</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="3"/>
+        <v>-0.94880119190988976</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
         <v>6</v>
       </c>
@@ -1589,7 +2111,7 @@
         <v>43</v>
       </c>
       <c r="E47">
-        <f>EXP(2-1.2*(LN(F47)-LN(AVERAGE(F:F)))+0.02*H47)</f>
+        <f t="shared" si="5"/>
         <v>7.3374262534090731</v>
       </c>
       <c r="F47">
@@ -1599,11 +2121,23 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>7.661290280520916</v>
       </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L47">
+        <f t="shared" si="1"/>
+        <v>1.992988134460991</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="3"/>
+        <v>-1.1020269975203083</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
         <v>6</v>
       </c>
@@ -1614,7 +2148,7 @@
         <v>44</v>
       </c>
       <c r="E48">
-        <f>EXP(2-1.2*(LN(F48)-LN(AVERAGE(F:F)))+0.02*H48)</f>
+        <f t="shared" si="5"/>
         <v>6.7962788309619482</v>
       </c>
       <c r="F48">
@@ -1624,11 +2158,23 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.830645140260458</v>
       </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L48">
+        <f t="shared" si="1"/>
+        <v>1.9163752316557818</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="3"/>
+        <v>-1.1786399003255175</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" t="s">
         <v>6</v>
       </c>
@@ -1639,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="E49">
-        <f>EXP(2-1.2*(LN(F49)-LN(AVERAGE(F:F)))+0.02*H49)</f>
+        <f t="shared" si="5"/>
         <v>6.5408608173347185</v>
       </c>
       <c r="F49">
@@ -1649,11 +2195,23 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.915322570130229</v>
       </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L49">
+        <f t="shared" si="1"/>
+        <v>1.8780687802531773</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="3"/>
+        <v>-1.216946351728122</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" t="s">
         <v>6</v>
       </c>
@@ -1664,7 +2222,7 @@
         <v>46</v>
       </c>
       <c r="E50">
-        <f>EXP(2-1.2*(LN(F50)-LN(AVERAGE(F:F)))+0.02*H50)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F50">
@@ -1674,11 +2232,23 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
         <v>6</v>
       </c>
@@ -1689,7 +2259,7 @@
         <v>47</v>
       </c>
       <c r="E51">
-        <f>EXP(2-1.2*(LN(F51)-LN(AVERAGE(F:F)))+0.02*H51)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F51">
@@ -1699,11 +2269,23 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
         <v>6</v>
       </c>
@@ -1714,7 +2296,7 @@
         <v>48</v>
       </c>
       <c r="E52">
-        <f>EXP(2-1.2*(LN(F52)-LN(AVERAGE(F:F)))+0.02*H52)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F52">
@@ -1724,11 +2306,23 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" t="s">
         <v>6</v>
       </c>
@@ -1739,7 +2333,7 @@
         <v>49</v>
       </c>
       <c r="E53">
-        <f>EXP(2-1.2*(LN(F53)-LN(AVERAGE(F:F)))+0.02*H53)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F53">
@@ -1749,11 +2343,23 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" t="s">
         <v>6</v>
       </c>
@@ -1764,7 +2370,7 @@
         <v>50</v>
       </c>
       <c r="E54">
-        <f>EXP(2-1.2*(LN(F54)-LN(AVERAGE(F:F)))+0.02*H54)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F54">
@@ -1774,11 +2380,23 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" t="s">
         <v>6</v>
       </c>
@@ -1789,7 +2407,7 @@
         <v>51</v>
       </c>
       <c r="E55">
-        <f>EXP(2-1.2*(LN(F55)-LN(AVERAGE(F:F)))+0.02*H55)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F55">
@@ -1799,11 +2417,23 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" t="s">
         <v>6</v>
       </c>
@@ -1814,7 +2444,7 @@
         <v>52</v>
       </c>
       <c r="E56">
-        <f>EXP(2-1.2*(LN(F56)-LN(AVERAGE(F:F)))+0.02*H56)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F56">
@@ -1824,11 +2454,23 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" t="s">
         <v>6</v>
       </c>
@@ -1839,7 +2481,7 @@
         <v>53</v>
       </c>
       <c r="E57">
-        <f>EXP(2-1.2*(LN(F57)-LN(AVERAGE(F:F)))+0.02*H57)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F57">
@@ -1849,11 +2491,23 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" t="s">
         <v>6</v>
       </c>
@@ -1864,7 +2518,7 @@
         <v>54</v>
       </c>
       <c r="E58">
-        <f>EXP(2-1.2*(LN(F58)-LN(AVERAGE(F:F)))+0.02*H58)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F58">
@@ -1874,11 +2528,23 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" t="s">
         <v>6</v>
       </c>
@@ -1889,7 +2555,7 @@
         <v>55</v>
       </c>
       <c r="E59">
-        <f>EXP(2-1.2*(LN(F59)-LN(AVERAGE(F:F)))+0.02*H59)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F59">
@@ -1899,11 +2565,23 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" t="s">
         <v>6</v>
       </c>
@@ -1914,7 +2592,7 @@
         <v>56</v>
       </c>
       <c r="E60">
-        <f>EXP(2-1.2*(LN(F60)-LN(AVERAGE(F:F)))+0.02*H60)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F60">
@@ -1924,11 +2602,23 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -1939,7 +2629,7 @@
         <v>57</v>
       </c>
       <c r="E61">
-        <f>EXP(2-1.2*(LN(F61)-LN(AVERAGE(F:F)))+0.02*H61)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F61">
@@ -1949,11 +2639,23 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" t="s">
         <v>6</v>
       </c>
@@ -1964,7 +2666,7 @@
         <v>58</v>
       </c>
       <c r="E62">
-        <f>EXP(2-1.2*(LN(F62)-LN(AVERAGE(F:F)))+0.02*H62)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F62">
@@ -1974,11 +2676,23 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" t="s">
         <v>6</v>
       </c>
@@ -1989,7 +2703,7 @@
         <v>59</v>
       </c>
       <c r="E63">
-        <f>EXP(2-1.2*(LN(F63)-LN(AVERAGE(F:F)))+0.02*H63)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F63">
@@ -1999,11 +2713,23 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" t="s">
         <v>6</v>
       </c>
@@ -2014,7 +2740,7 @@
         <v>60</v>
       </c>
       <c r="E64">
-        <f>EXP(2-1.2*(LN(F64)-LN(AVERAGE(F:F)))+0.02*H64)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F64">
@@ -2024,11 +2750,23 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" t="s">
         <v>6</v>
       </c>
@@ -2039,7 +2777,7 @@
         <v>61</v>
       </c>
       <c r="E65">
-        <f>EXP(2-1.2*(LN(F65)-LN(AVERAGE(F:F)))+0.02*H65)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F65">
@@ -2049,11 +2787,23 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" t="s">
         <v>6</v>
       </c>
@@ -2064,7 +2814,7 @@
         <v>62</v>
       </c>
       <c r="E66">
-        <f>EXP(2-1.2*(LN(F66)-LN(AVERAGE(F:F)))+0.02*H66)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F66">
@@ -2074,11 +2824,23 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" t="s">
         <v>6</v>
       </c>
@@ -2089,7 +2851,7 @@
         <v>63</v>
       </c>
       <c r="E67">
-        <f>EXP(2-1.2*(LN(F67)-LN(AVERAGE(F:F)))+0.02*H67)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F67">
@@ -2099,11 +2861,23 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" t="s">
         <v>6</v>
       </c>
@@ -2114,7 +2888,7 @@
         <v>64</v>
       </c>
       <c r="E68">
-        <f>EXP(2-1.2*(LN(F68)-LN(AVERAGE(F:F)))+0.02*H68)</f>
+        <f t="shared" si="5"/>
         <v>6.2950419333647467</v>
       </c>
       <c r="F68">
@@ -2124,11 +2898,23 @@
         <v>0</v>
       </c>
       <c r="H68">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" t="s">
         <v>6</v>
       </c>
@@ -2139,7 +2925,7 @@
         <v>65</v>
       </c>
       <c r="E69">
-        <f>EXP(2-1.2*(LN(F69)-LN(AVERAGE(F:F)))+0.02*H69)</f>
+        <f t="shared" ref="E69:E100" si="6">EXP(2-1.2*(LN(F69)-LN(AVERAGE(F:F)))+0.02*H69)</f>
         <v>6.2950419333647467</v>
       </c>
       <c r="F69">
@@ -2149,11 +2935,23 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="1"/>
+        <v>1.8397623288505727</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="2"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="3"/>
+        <v>-1.2552528031307266</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" t="s">
         <v>6</v>
       </c>
@@ -2164,7 +2962,7 @@
         <v>66</v>
       </c>
       <c r="E70">
-        <f>EXP(2-1.2*(LN(F70)-LN(AVERAGE(F:F)))+0.02*H70)</f>
+        <f t="shared" si="6"/>
         <v>28.212420630080594</v>
       </c>
       <c r="F70">
@@ -2174,11 +2972,23 @@
         <v>75</v>
       </c>
       <c r="H70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L70">
+        <f t="shared" ref="L70:L133" si="7">LN(E70)</f>
+        <v>3.3397623288505729</v>
+      </c>
+      <c r="M70">
+        <f t="shared" ref="M70:M108" si="8">AVERAGE($L$5:$L$108)</f>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N70">
+        <f t="shared" ref="N70:N133" si="9">L70-M70</f>
+        <v>0.2447471968692736</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
         <v>6</v>
       </c>
@@ -2189,7 +2999,7 @@
         <v>67</v>
       </c>
       <c r="E71">
-        <f>EXP(2-1.2*(LN(F71)-LN(AVERAGE(F:F)))+0.02*H71)</f>
+        <f t="shared" si="6"/>
         <v>59.725694942564381</v>
       </c>
       <c r="F71">
@@ -2199,11 +3009,23 @@
         <v>75</v>
       </c>
       <c r="H71">
-        <f t="shared" ref="H71:H108" si="1">IF(H70*0.5&gt;1,G71+H70*0.5,G71)</f>
+        <f t="shared" ref="H71:H108" si="10">IF(H70*0.5&gt;1,G71+H70*0.5,G71)</f>
         <v>112.5</v>
       </c>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L71">
+        <f t="shared" si="7"/>
+        <v>4.0897623288505729</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="9"/>
+        <v>0.9947471968692736</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" t="s">
         <v>6</v>
       </c>
@@ -2214,7 +3036,7 @@
         <v>68</v>
       </c>
       <c r="E72">
-        <f>EXP(2-1.2*(LN(F72)-LN(AVERAGE(F:F)))+0.02*H72)</f>
+        <f t="shared" si="6"/>
         <v>86.900373373536894</v>
       </c>
       <c r="F72">
@@ -2224,11 +3046,23 @@
         <v>75</v>
       </c>
       <c r="H72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>131.25</v>
       </c>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L72">
+        <f t="shared" si="7"/>
+        <v>4.4647623288505729</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="9"/>
+        <v>1.3697471968692736</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
         <v>6</v>
       </c>
@@ -2239,7 +3073,7 @@
         <v>69</v>
       </c>
       <c r="E73">
-        <f>EXP(2-1.2*(LN(F73)-LN(AVERAGE(F:F)))+0.02*H73)</f>
+        <f t="shared" si="6"/>
         <v>23.388918196690248</v>
       </c>
       <c r="F73">
@@ -2249,11 +3083,23 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>65.625</v>
       </c>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L73">
+        <f t="shared" si="7"/>
+        <v>3.1522623288505729</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="9"/>
+        <v>5.7247196869273598E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
         <v>6</v>
       </c>
@@ -2264,7 +3110,7 @@
         <v>70</v>
       </c>
       <c r="E74">
-        <f>EXP(2-1.2*(LN(F74)-LN(AVERAGE(F:F)))+0.02*H74)</f>
+        <f t="shared" si="6"/>
         <v>12.134010912480791</v>
       </c>
       <c r="F74">
@@ -2274,11 +3120,23 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>32.8125</v>
       </c>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L74">
+        <f t="shared" si="7"/>
+        <v>2.4960123288505729</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="9"/>
+        <v>-0.5990028031307264</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
         <v>6</v>
       </c>
@@ -2289,7 +3147,7 @@
         <v>71</v>
       </c>
       <c r="E75">
-        <f>EXP(2-1.2*(LN(F75)-LN(AVERAGE(F:F)))+0.02*H75)</f>
+        <f t="shared" si="6"/>
         <v>39.169067027651067</v>
       </c>
       <c r="F75">
@@ -2299,11 +3157,23 @@
         <v>75</v>
       </c>
       <c r="H75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>91.40625</v>
       </c>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L75">
+        <f t="shared" si="7"/>
+        <v>3.6678873288505729</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="9"/>
+        <v>0.5728721968692736</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
         <v>6</v>
       </c>
@@ -2314,7 +3184,7 @@
         <v>72</v>
       </c>
       <c r="E76">
-        <f>EXP(2-1.2*(LN(F76)-LN(AVERAGE(F:F)))+0.02*H76)</f>
+        <f t="shared" si="6"/>
         <v>70.374067001931479</v>
       </c>
       <c r="F76">
@@ -2324,11 +3194,23 @@
         <v>75</v>
       </c>
       <c r="H76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>120.703125</v>
       </c>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L76">
+        <f t="shared" si="7"/>
+        <v>4.2538248288505729</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="9"/>
+        <v>1.1588096968692736</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
         <v>6</v>
       </c>
@@ -2339,7 +3221,7 @@
         <v>73</v>
       </c>
       <c r="E77">
-        <f>EXP(2-1.2*(LN(F77)-LN(AVERAGE(F:F)))+0.02*H77)</f>
+        <f t="shared" si="6"/>
         <v>94.329462904319612</v>
       </c>
       <c r="F77">
@@ -2349,11 +3231,23 @@
         <v>75</v>
       </c>
       <c r="H77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>135.3515625</v>
       </c>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L77">
+        <f t="shared" si="7"/>
+        <v>4.5467935788505729</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="9"/>
+        <v>1.4517784468692736</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
         <v>6</v>
       </c>
@@ -2364,7 +3258,7 @@
         <v>74</v>
       </c>
       <c r="E78">
-        <f>EXP(2-1.2*(LN(F78)-LN(AVERAGE(F:F)))+0.02*H78)</f>
+        <f t="shared" si="6"/>
         <v>24.368174419403402</v>
       </c>
       <c r="F78">
@@ -2374,11 +3268,23 @@
         <v>0</v>
       </c>
       <c r="H78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>67.67578125</v>
       </c>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L78">
+        <f t="shared" si="7"/>
+        <v>3.1932779538505729</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="9"/>
+        <v>9.8262821869273598E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
         <v>6</v>
       </c>
@@ -2389,7 +3295,7 @@
         <v>75</v>
       </c>
       <c r="E79">
-        <f>EXP(2-1.2*(LN(F79)-LN(AVERAGE(F:F)))+0.02*H79)</f>
+        <f t="shared" si="6"/>
         <v>12.385422068290229</v>
       </c>
       <c r="F79">
@@ -2399,11 +3305,23 @@
         <v>0</v>
       </c>
       <c r="H79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>33.837890625</v>
       </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L79">
+        <f t="shared" si="7"/>
+        <v>2.5165201413505729</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="9"/>
+        <v>-0.5784949906307264</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
         <v>6</v>
       </c>
@@ -2414,7 +3332,7 @@
         <v>76</v>
       </c>
       <c r="E80">
-        <f>EXP(2-1.2*(LN(F80)-LN(AVERAGE(F:F)))+0.02*H80)</f>
+        <f t="shared" si="6"/>
         <v>39.572769193749757</v>
       </c>
       <c r="F80">
@@ -2424,11 +3342,23 @@
         <v>75</v>
       </c>
       <c r="H80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>91.9189453125</v>
       </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L80">
+        <f t="shared" si="7"/>
+        <v>3.6781412351005729</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="9"/>
+        <v>0.5831261031192736</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" t="s">
         <v>6</v>
       </c>
@@ -2439,7 +3369,7 @@
         <v>77</v>
       </c>
       <c r="E81">
-        <f>EXP(2-1.2*(LN(F81)-LN(AVERAGE(F:F)))+0.02*H81)</f>
+        <f t="shared" si="6"/>
         <v>70.73579804134657</v>
       </c>
       <c r="F81">
@@ -2449,11 +3379,23 @@
         <v>75</v>
       </c>
       <c r="H81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>120.95947265625</v>
       </c>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L81">
+        <f t="shared" si="7"/>
+        <v>4.2589517819755729</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="9"/>
+        <v>1.1639366499942736</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
         <v>6</v>
       </c>
@@ -2464,7 +3406,7 @@
         <v>78</v>
       </c>
       <c r="E82">
-        <f>EXP(2-1.2*(LN(F82)-LN(AVERAGE(F:F)))+0.02*H82)</f>
+        <f t="shared" si="6"/>
         <v>94.571584475524546</v>
       </c>
       <c r="F82">
@@ -2474,11 +3416,23 @@
         <v>75</v>
       </c>
       <c r="H82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>135.479736328125</v>
       </c>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L82">
+        <f t="shared" si="7"/>
+        <v>4.5493570554130729</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="9"/>
+        <v>1.4543419234317736</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
         <v>6</v>
       </c>
@@ -2489,7 +3443,7 @@
         <v>79</v>
       </c>
       <c r="E83">
-        <f>EXP(2-1.2*(LN(F83)-LN(AVERAGE(F:F)))+0.02*H83)</f>
+        <f t="shared" si="6"/>
         <v>24.399428066620199</v>
       </c>
       <c r="F83">
@@ -2499,11 +3453,23 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>67.7398681640625</v>
       </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L83">
+        <f t="shared" si="7"/>
+        <v>3.1945596921318229</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="9"/>
+        <v>9.9544560150523598E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" t="s">
         <v>6</v>
       </c>
@@ -2514,7 +3480,7 @@
         <v>80</v>
       </c>
       <c r="E84">
-        <f>EXP(2-1.2*(LN(F84)-LN(AVERAGE(F:F)))+0.02*H84)</f>
+        <f t="shared" si="6"/>
         <v>12.393362047059343</v>
       </c>
       <c r="F84">
@@ -2524,11 +3490,23 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>33.86993408203125</v>
       </c>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L84">
+        <f t="shared" si="7"/>
+        <v>2.5171610104911979</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="9"/>
+        <v>-0.5778541214901014</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
         <v>6</v>
       </c>
@@ -2539,7 +3517,7 @@
         <v>81</v>
       </c>
       <c r="E85">
-        <f>EXP(2-1.2*(LN(F85)-LN(AVERAGE(F:F)))+0.02*H85)</f>
+        <f t="shared" si="6"/>
         <v>39.585451708892059</v>
       </c>
       <c r="F85">
@@ -2549,11 +3527,23 @@
         <v>75</v>
       </c>
       <c r="H85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>91.934967041015625</v>
       </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L85">
+        <f t="shared" si="7"/>
+        <v>3.6784616696708854</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="9"/>
+        <v>0.5834465376895861</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
         <v>6</v>
       </c>
@@ -2564,7 +3554,7 @@
         <v>82</v>
       </c>
       <c r="E86">
-        <f>EXP(2-1.2*(LN(F86)-LN(AVERAGE(F:F)))+0.02*H86)</f>
+        <f t="shared" si="6"/>
         <v>70.747132046799663</v>
       </c>
       <c r="F86">
@@ -2574,11 +3564,23 @@
         <v>75</v>
       </c>
       <c r="H86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>120.96748352050781</v>
       </c>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L86">
+        <f t="shared" si="7"/>
+        <v>4.2591119992607291</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="9"/>
+        <v>1.1640968672794298</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
         <v>6</v>
       </c>
@@ -2589,7 +3591,7 @@
         <v>83</v>
       </c>
       <c r="E87">
-        <f>EXP(2-1.2*(LN(F87)-LN(AVERAGE(F:F)))+0.02*H87)</f>
+        <f t="shared" si="6"/>
         <v>94.579160780243029</v>
       </c>
       <c r="F87">
@@ -2599,11 +3601,23 @@
         <v>75</v>
       </c>
       <c r="H87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>135.48374176025391</v>
       </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L87">
+        <f t="shared" si="7"/>
+        <v>4.549437164055651</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="9"/>
+        <v>1.4544220320743517</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
         <v>6</v>
       </c>
@@ -2614,7 +3628,7 @@
         <v>84</v>
       </c>
       <c r="E88">
-        <f>EXP(2-1.2*(LN(F88)-LN(AVERAGE(F:F)))+0.02*H88)</f>
+        <f t="shared" si="6"/>
         <v>24.400405388724106</v>
       </c>
       <c r="F88">
@@ -2624,11 +3638,23 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>67.741870880126953</v>
       </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L88">
+        <f t="shared" si="7"/>
+        <v>3.194599746453112</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="9"/>
+        <v>9.958461447181266E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
         <v>6</v>
       </c>
@@ -2639,7 +3665,7 @@
         <v>85</v>
       </c>
       <c r="E89">
-        <f>EXP(2-1.2*(LN(F89)-LN(AVERAGE(F:F)))+0.02*H89)</f>
+        <f t="shared" si="6"/>
         <v>12.39361025339741</v>
       </c>
       <c r="F89">
@@ -2649,11 +3675,23 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>33.870935440063477</v>
       </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L89">
+        <f t="shared" si="7"/>
+        <v>2.5171810376518424</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="9"/>
+        <v>-0.57783409432945687</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
         <v>6</v>
       </c>
@@ -2664,7 +3702,7 @@
         <v>86</v>
       </c>
       <c r="E90">
-        <f>EXP(2-1.2*(LN(F90)-LN(AVERAGE(F:F)))+0.02*H90)</f>
+        <f t="shared" si="6"/>
         <v>39.585848102976996</v>
       </c>
       <c r="F90">
@@ -2674,11 +3712,23 @@
         <v>75</v>
       </c>
       <c r="H90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>91.935467720031738</v>
       </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L90">
+        <f t="shared" si="7"/>
+        <v>3.6784716832512077</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="9"/>
+        <v>0.58345655126990836</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
         <v>6</v>
       </c>
@@ -2689,7 +3739,7 @@
         <v>87</v>
       </c>
       <c r="E91">
-        <f>EXP(2-1.2*(LN(F91)-LN(AVERAGE(F:F)))+0.02*H91)</f>
+        <f t="shared" si="6"/>
         <v>70.747486263731076</v>
       </c>
       <c r="F91">
@@ -2699,11 +3749,23 @@
         <v>75</v>
       </c>
       <c r="H91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>120.96773386001587</v>
       </c>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L91">
+        <f t="shared" si="7"/>
+        <v>4.2591170060508903</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="9"/>
+        <v>1.164101874069591</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
         <v>6</v>
       </c>
@@ -2714,7 +3776,7 @@
         <v>88</v>
       </c>
       <c r="E92">
-        <f>EXP(2-1.2*(LN(F92)-LN(AVERAGE(F:F)))+0.02*H92)</f>
+        <f t="shared" si="6"/>
         <v>94.579397549545206</v>
       </c>
       <c r="F92">
@@ -2724,11 +3786,23 @@
         <v>75</v>
       </c>
       <c r="H92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>135.48386693000793</v>
       </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L92">
+        <f t="shared" si="7"/>
+        <v>4.5494396674507316</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="9"/>
+        <v>1.4544245354694323</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
         <v>6</v>
       </c>
@@ -2739,7 +3813,7 @@
         <v>89</v>
       </c>
       <c r="E93">
-        <f>EXP(2-1.2*(LN(F93)-LN(AVERAGE(F:F)))+0.02*H93)</f>
+        <f t="shared" si="6"/>
         <v>24.400435930670628</v>
       </c>
       <c r="F93">
@@ -2749,11 +3823,23 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>67.741933465003967</v>
       </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L93">
+        <f t="shared" si="7"/>
+        <v>3.1946009981506522</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="9"/>
+        <v>9.9585866169352943E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" t="s">
         <v>6</v>
       </c>
@@ -2764,7 +3850,7 @@
         <v>90</v>
       </c>
       <c r="E94">
-        <f>EXP(2-1.2*(LN(F94)-LN(AVERAGE(F:F)))+0.02*H94)</f>
+        <f t="shared" si="6"/>
         <v>16.199071488607149</v>
       </c>
       <c r="F94">
@@ -2774,11 +3860,23 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>33.870966732501984</v>
       </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L94">
+        <f t="shared" si="7"/>
+        <v>2.784953925077664</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="9"/>
+        <v>-0.31006120690363526</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
         <v>6</v>
       </c>
@@ -2789,7 +3887,7 @@
         <v>91</v>
       </c>
       <c r="E95">
-        <f>EXP(2-1.2*(LN(F95)-LN(AVERAGE(F:F)))+0.02*H95)</f>
+        <f t="shared" si="6"/>
         <v>51.74067681509564</v>
       </c>
       <c r="F95">
@@ -2799,11 +3897,23 @@
         <v>75</v>
       </c>
       <c r="H95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>91.935483366250992</v>
       </c>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L95">
+        <f t="shared" si="7"/>
+        <v>3.9462442577526442</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="9"/>
+        <v>0.85122912577134491</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" t="s">
         <v>6</v>
       </c>
@@ -2814,7 +3924,7 @@
         <v>92</v>
       </c>
       <c r="E96">
-        <f>EXP(2-1.2*(LN(F96)-LN(AVERAGE(F:F)))+0.02*H96)</f>
+        <f t="shared" si="6"/>
         <v>20.632952302481655</v>
       </c>
       <c r="F96">
@@ -2824,11 +3934,23 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>45.967741683125496</v>
       </c>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L96">
+        <f t="shared" si="7"/>
+        <v>3.0268894240901343</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="9"/>
+        <v>-6.812570789116501E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" t="s">
         <v>6</v>
       </c>
@@ -2839,7 +3961,7 @@
         <v>93</v>
       </c>
       <c r="E97">
-        <f>EXP(2-1.2*(LN(F97)-LN(AVERAGE(F:F)))+0.02*H97)</f>
+        <f t="shared" si="6"/>
         <v>13.029447749774633</v>
       </c>
       <c r="F97">
@@ -2849,11 +3971,23 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>22.983870841562748</v>
       </c>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L97">
+        <f t="shared" si="7"/>
+        <v>2.5672120072588793</v>
+      </c>
+      <c r="M97">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N97">
+        <f t="shared" si="9"/>
+        <v>-0.52780312472241997</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" t="s">
         <v>6</v>
       </c>
@@ -2864,7 +3998,7 @@
         <v>94</v>
       </c>
       <c r="E98">
-        <f>EXP(2-1.2*(LN(F98)-LN(AVERAGE(F:F)))+0.02*H98)</f>
+        <f t="shared" si="6"/>
         <v>10.354003938284865</v>
       </c>
       <c r="F98">
@@ -2874,11 +4008,23 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>11.491935420781374</v>
       </c>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L98">
+        <f t="shared" si="7"/>
+        <v>2.3373732988432518</v>
+      </c>
+      <c r="M98">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N98">
+        <f t="shared" si="9"/>
+        <v>-0.75764183313804745</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
         <v>6</v>
       </c>
@@ -2889,7 +4035,7 @@
         <v>95</v>
       </c>
       <c r="E99">
-        <f>EXP(2-1.2*(LN(F99)-LN(AVERAGE(F:F)))+0.02*H99)</f>
+        <f t="shared" si="6"/>
         <v>9.2299528913140705</v>
       </c>
       <c r="F99">
@@ -2899,11 +4045,23 @@
         <v>0</v>
       </c>
       <c r="H99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>5.745967710390687</v>
       </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L99">
+        <f t="shared" si="7"/>
+        <v>2.2224539446354381</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N99">
+        <f t="shared" si="9"/>
+        <v>-0.87256118734586119</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
         <v>6</v>
       </c>
@@ -2914,7 +4072,7 @@
         <v>96</v>
       </c>
       <c r="E100">
-        <f>EXP(2-1.2*(LN(F100)-LN(AVERAGE(F:F)))+0.02*H100)</f>
+        <f t="shared" si="6"/>
         <v>8.7145519608137203</v>
       </c>
       <c r="F100">
@@ -2924,11 +4082,23 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.8729838551953435</v>
       </c>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L100">
+        <f t="shared" si="7"/>
+        <v>2.1649942675315312</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N100">
+        <f t="shared" si="9"/>
+        <v>-0.93002086444976806</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" t="s">
         <v>6</v>
       </c>
@@ -2939,7 +4109,7 @@
         <v>97</v>
       </c>
       <c r="E101">
-        <f>EXP(2-1.2*(LN(F101)-LN(AVERAGE(F:F)))+0.02*H101)</f>
+        <f t="shared" ref="E101:E132" si="11">EXP(2-1.2*(LN(F101)-LN(AVERAGE(F:F)))+0.02*H101)</f>
         <v>8.4677466048778829</v>
       </c>
       <c r="F101">
@@ -2949,11 +4119,23 @@
         <v>0</v>
       </c>
       <c r="H101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>1.4364919275976717</v>
       </c>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L101">
+        <f t="shared" si="7"/>
+        <v>2.1362644289795778</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N101">
+        <f t="shared" si="9"/>
+        <v>-0.95875070300172149</v>
+      </c>
+    </row>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" t="s">
         <v>6</v>
       </c>
@@ -2964,7 +4146,7 @@
         <v>98</v>
       </c>
       <c r="E102">
-        <f>EXP(2-1.2*(LN(F102)-LN(AVERAGE(F:F)))+0.02*H102)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F102">
@@ -2974,11 +4156,23 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M102">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N102">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" t="s">
         <v>6</v>
       </c>
@@ -2989,7 +4183,7 @@
         <v>99</v>
       </c>
       <c r="E103">
-        <f>EXP(2-1.2*(LN(F103)-LN(AVERAGE(F:F)))+0.02*H103)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F103">
@@ -2999,11 +4193,23 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N103">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" t="s">
         <v>6</v>
       </c>
@@ -3014,7 +4220,7 @@
         <v>100</v>
       </c>
       <c r="E104">
-        <f>EXP(2-1.2*(LN(F104)-LN(AVERAGE(F:F)))+0.02*H104)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F104">
@@ -3024,11 +4230,23 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" t="s">
         <v>6</v>
       </c>
@@ -3039,7 +4257,7 @@
         <v>101</v>
       </c>
       <c r="E105">
-        <f>EXP(2-1.2*(LN(F105)-LN(AVERAGE(F:F)))+0.02*H105)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F105">
@@ -3049,11 +4267,23 @@
         <v>0</v>
       </c>
       <c r="H105">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N105">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" t="s">
         <v>6</v>
       </c>
@@ -3064,7 +4294,7 @@
         <v>102</v>
       </c>
       <c r="E106">
-        <f>EXP(2-1.2*(LN(F106)-LN(AVERAGE(F:F)))+0.02*H106)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F106">
@@ -3074,11 +4304,23 @@
         <v>0</v>
       </c>
       <c r="H106">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N106">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" t="s">
         <v>6</v>
       </c>
@@ -3089,7 +4331,7 @@
         <v>103</v>
       </c>
       <c r="E107">
-        <f>EXP(2-1.2*(LN(F107)-LN(AVERAGE(F:F)))+0.02*H107)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F107">
@@ -3099,11 +4341,23 @@
         <v>0</v>
       </c>
       <c r="H107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M107">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N107">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" t="s">
         <v>6</v>
       </c>
@@ -3114,7 +4368,7 @@
         <v>104</v>
       </c>
       <c r="E108">
-        <f>EXP(2-1.2*(LN(F108)-LN(AVERAGE(F:F)))+0.02*H108)</f>
+        <f t="shared" si="11"/>
         <v>8.2279310384335211</v>
       </c>
       <c r="F108">
@@ -3124,11 +4378,23 @@
         <v>0</v>
       </c>
       <c r="H108">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <f t="shared" si="7"/>
+        <v>2.1075345904276244</v>
+      </c>
+      <c r="M108">
+        <f t="shared" si="8"/>
+        <v>3.0950151319812993</v>
+      </c>
+      <c r="N108">
+        <f t="shared" si="9"/>
+        <v>-0.98748054155367493</v>
+      </c>
+    </row>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="E109">
-        <f>EXP(3-1.2*(LN(F109)-LN(AVERAGE(F:F)))+0.02*H109)</f>
+        <f t="shared" ref="E109:E140" si="12">EXP(3-1.2*(LN(F109)-LN(AVERAGE(F:F)))+0.02*H109)</f>
         <v>27.835730314941824</v>
       </c>
       <c r="F109">
@@ -3152,8 +4418,20 @@
         <f>G109</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L109">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M109">
+        <f>AVERAGE($L$109:$L$212)</f>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N109">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" t="s">
         <v>8</v>
       </c>
@@ -3164,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="E110">
-        <f>EXP(3-1.2*(LN(F110)-LN(AVERAGE(F:F)))+0.02*H110)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F110">
@@ -3177,8 +4455,20 @@
         <f>IF(H109*0.5&gt;1,G110+H109*0.5,G110)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L110">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M110">
+        <f t="shared" ref="M110:M173" si="13">AVERAGE($L$109:$L$212)</f>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N110">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" t="s">
         <v>8</v>
       </c>
@@ -3189,7 +4479,7 @@
         <v>3</v>
       </c>
       <c r="E111">
-        <f>EXP(3-1.2*(LN(F111)-LN(AVERAGE(F:F)))+0.02*H111)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F111">
@@ -3199,11 +4489,23 @@
         <v>0</v>
       </c>
       <c r="H111">
-        <f t="shared" ref="H111:H174" si="2">IF(H110*0.5&gt;1,G111+H110*0.5,G111)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" ref="H111:H174" si="14">IF(H110*0.5&gt;1,G111+H110*0.5,G111)</f>
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M111">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N111">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" t="s">
         <v>8</v>
       </c>
@@ -3214,7 +4516,7 @@
         <v>4</v>
       </c>
       <c r="E112">
-        <f>EXP(3-1.2*(LN(F112)-LN(AVERAGE(F:F)))+0.02*H112)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F112">
@@ -3224,11 +4526,23 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M112">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N112">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" t="s">
         <v>8</v>
       </c>
@@ -3239,7 +4553,7 @@
         <v>5</v>
       </c>
       <c r="E113">
-        <f>EXP(3-1.2*(LN(F113)-LN(AVERAGE(F:F)))+0.02*H113)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F113">
@@ -3249,11 +4563,23 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M113">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N113">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" t="s">
         <v>8</v>
       </c>
@@ -3264,7 +4590,7 @@
         <v>6</v>
       </c>
       <c r="E114">
-        <f>EXP(3-1.2*(LN(F114)-LN(AVERAGE(F:F)))+0.02*H114)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F114">
@@ -3274,11 +4600,23 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M114">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N114">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" t="s">
         <v>8</v>
       </c>
@@ -3289,7 +4627,7 @@
         <v>7</v>
       </c>
       <c r="E115">
-        <f>EXP(3-1.2*(LN(F115)-LN(AVERAGE(F:F)))+0.02*H115)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F115">
@@ -3299,11 +4637,23 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M115">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N115">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="116" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" t="s">
         <v>8</v>
       </c>
@@ -3314,7 +4664,7 @@
         <v>8</v>
       </c>
       <c r="E116">
-        <f>EXP(3-1.2*(LN(F116)-LN(AVERAGE(F:F)))+0.02*H116)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F116">
@@ -3324,11 +4674,23 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M116">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N116">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" t="s">
         <v>8</v>
       </c>
@@ -3339,7 +4701,7 @@
         <v>9</v>
       </c>
       <c r="E117">
-        <f>EXP(3-1.2*(LN(F117)-LN(AVERAGE(F:F)))+0.02*H117)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F117">
@@ -3349,11 +4711,23 @@
         <v>0</v>
       </c>
       <c r="H117">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M117">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N117">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="118" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" t="s">
         <v>8</v>
       </c>
@@ -3364,7 +4738,7 @@
         <v>10</v>
       </c>
       <c r="E118">
-        <f>EXP(3-1.2*(LN(F118)-LN(AVERAGE(F:F)))+0.02*H118)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F118">
@@ -3374,11 +4748,23 @@
         <v>0</v>
       </c>
       <c r="H118">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M118">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N118">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" t="s">
         <v>8</v>
       </c>
@@ -3389,7 +4775,7 @@
         <v>11</v>
       </c>
       <c r="E119">
-        <f>EXP(3-1.2*(LN(F119)-LN(AVERAGE(F:F)))+0.02*H119)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F119">
@@ -3399,11 +4785,23 @@
         <v>0</v>
       </c>
       <c r="H119">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M119">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N119">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" t="s">
         <v>8</v>
       </c>
@@ -3414,7 +4812,7 @@
         <v>12</v>
       </c>
       <c r="E120">
-        <f>EXP(3-1.2*(LN(F120)-LN(AVERAGE(F:F)))+0.02*H120)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F120">
@@ -3424,11 +4822,23 @@
         <v>0</v>
       </c>
       <c r="H120">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M120">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" t="s">
         <v>8</v>
       </c>
@@ -3439,7 +4849,7 @@
         <v>13</v>
       </c>
       <c r="E121">
-        <f>EXP(3-1.2*(LN(F121)-LN(AVERAGE(F:F)))+0.02*H121)</f>
+        <f t="shared" si="12"/>
         <v>27.835730314941824</v>
       </c>
       <c r="F121">
@@ -3449,11 +4859,23 @@
         <v>0</v>
       </c>
       <c r="H121">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <f t="shared" si="7"/>
+        <v>3.3263204585803696</v>
+      </c>
+      <c r="M121">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N121">
+        <f t="shared" si="9"/>
+        <v>-0.76869467340092479</v>
+      </c>
+    </row>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" t="s">
         <v>8</v>
       </c>
@@ -3464,7 +4886,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <f>EXP(3-1.2*(LN(F122)-LN(AVERAGE(F:F)))+0.02*H122)</f>
+        <f t="shared" si="12"/>
         <v>205.67977285180959</v>
       </c>
       <c r="F122">
@@ -3474,11 +4896,23 @@
         <v>100</v>
       </c>
       <c r="H122">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L122">
+        <f t="shared" si="7"/>
+        <v>5.3263204585803692</v>
+      </c>
+      <c r="M122">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N122">
+        <f t="shared" si="9"/>
+        <v>1.2313053265990748</v>
+      </c>
+    </row>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" t="s">
         <v>8</v>
       </c>
@@ -3489,7 +4923,7 @@
         <v>15</v>
       </c>
       <c r="E123">
-        <f>EXP(3-1.2*(LN(F123)-LN(AVERAGE(F:F)))+0.02*H123)</f>
+        <f t="shared" si="12"/>
         <v>559.09558902465812</v>
       </c>
       <c r="F123">
@@ -3499,11 +4933,23 @@
         <v>100</v>
       </c>
       <c r="H123">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L123">
+        <f t="shared" si="7"/>
+        <v>6.3263204585803692</v>
+      </c>
+      <c r="M123">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N123">
+        <f t="shared" si="9"/>
+        <v>2.2313053265990748</v>
+      </c>
+    </row>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" t="s">
         <v>8</v>
       </c>
@@ -3514,7 +4960,7 @@
         <v>16</v>
       </c>
       <c r="E124">
-        <f>EXP(3-1.2*(LN(F124)-LN(AVERAGE(F:F)))+0.02*H124)</f>
+        <f t="shared" si="12"/>
         <v>921.7927899795709</v>
       </c>
       <c r="F124">
@@ -3524,11 +4970,23 @@
         <v>100</v>
       </c>
       <c r="H124">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L124">
+        <f t="shared" si="7"/>
+        <v>6.8263204585803692</v>
+      </c>
+      <c r="M124">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N124">
+        <f t="shared" si="9"/>
+        <v>2.7313053265990748</v>
+      </c>
+    </row>
+    <row r="125" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" t="s">
         <v>8</v>
       </c>
@@ -3539,7 +4997,7 @@
         <v>17</v>
       </c>
       <c r="E125">
-        <f>EXP(3-1.2*(LN(F125)-LN(AVERAGE(F:F)))+0.02*H125)</f>
+        <f t="shared" si="12"/>
         <v>160.18356815893799</v>
       </c>
       <c r="F125">
@@ -3549,11 +5007,23 @@
         <v>0</v>
       </c>
       <c r="H125">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>87.5</v>
       </c>
-    </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L125">
+        <f t="shared" si="7"/>
+        <v>5.0763204585803692</v>
+      </c>
+      <c r="M125">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N125">
+        <f t="shared" si="9"/>
+        <v>0.98130532659907477</v>
+      </c>
+    </row>
+    <row r="126" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" t="s">
         <v>8</v>
       </c>
@@ -3564,7 +5034,7 @@
         <v>18</v>
       </c>
       <c r="E126">
-        <f>EXP(3-1.2*(LN(F126)-LN(AVERAGE(F:F)))+0.02*H126)</f>
+        <f t="shared" si="12"/>
         <v>66.774445742044904</v>
       </c>
       <c r="F126">
@@ -3574,11 +5044,23 @@
         <v>0</v>
       </c>
       <c r="H126">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>43.75</v>
       </c>
-    </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L126">
+        <f t="shared" si="7"/>
+        <v>4.2013204585803692</v>
+      </c>
+      <c r="M126">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N126">
+        <f t="shared" si="9"/>
+        <v>0.10630532659907477</v>
+      </c>
+    </row>
+    <row r="127" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" t="s">
         <v>8</v>
       </c>
@@ -3589,7 +5071,7 @@
         <v>19</v>
       </c>
       <c r="E127">
-        <f>EXP(3-1.2*(LN(F127)-LN(AVERAGE(F:F)))+0.02*H127)</f>
+        <f t="shared" si="12"/>
         <v>318.56306400906891</v>
       </c>
       <c r="F127">
@@ -3599,11 +5081,23 @@
         <v>100</v>
       </c>
       <c r="H127">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>121.875</v>
       </c>
-    </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L127">
+        <f t="shared" si="7"/>
+        <v>5.7638204585803692</v>
+      </c>
+      <c r="M127">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N127">
+        <f t="shared" si="9"/>
+        <v>1.6688053265990748</v>
+      </c>
+    </row>
+    <row r="128" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" t="s">
         <v>8</v>
       </c>
@@ -3614,7 +5108,7 @@
         <v>20</v>
       </c>
       <c r="E128">
-        <f>EXP(3-1.2*(LN(F128)-LN(AVERAGE(F:F)))+0.02*H128)</f>
+        <f t="shared" si="12"/>
         <v>695.80570270451585</v>
       </c>
       <c r="F128">
@@ -3624,11 +5118,23 @@
         <v>100</v>
       </c>
       <c r="H128">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>160.9375</v>
       </c>
-    </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L128">
+        <f t="shared" si="7"/>
+        <v>6.5450704585803692</v>
+      </c>
+      <c r="M128">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N128">
+        <f t="shared" si="9"/>
+        <v>2.4500553265990748</v>
+      </c>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" t="s">
         <v>8</v>
       </c>
@@ -3639,7 +5145,7 @@
         <v>21</v>
       </c>
       <c r="E129">
-        <f>EXP(3-1.2*(LN(F129)-LN(AVERAGE(F:F)))+0.02*H129)</f>
+        <f t="shared" si="12"/>
         <v>1028.334167218417</v>
       </c>
       <c r="F129">
@@ -3649,11 +5155,23 @@
         <v>100</v>
       </c>
       <c r="H129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>180.46875</v>
       </c>
-    </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L129">
+        <f t="shared" si="7"/>
+        <v>6.9356954585803692</v>
+      </c>
+      <c r="M129">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N129">
+        <f t="shared" si="9"/>
+        <v>2.8406803265990748</v>
+      </c>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" t="s">
         <v>8</v>
       </c>
@@ -3664,7 +5182,7 @@
         <v>22</v>
       </c>
       <c r="E130">
-        <f>EXP(3-1.2*(LN(F130)-LN(AVERAGE(F:F)))+0.02*H130)</f>
+        <f t="shared" si="12"/>
         <v>169.18756618715256</v>
       </c>
       <c r="F130">
@@ -3674,11 +5192,23 @@
         <v>0</v>
       </c>
       <c r="H130">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>90.234375</v>
       </c>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L130">
+        <f t="shared" si="7"/>
+        <v>5.1310079585803692</v>
+      </c>
+      <c r="M130">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N130">
+        <f t="shared" si="9"/>
+        <v>1.0359928265990748</v>
+      </c>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" t="s">
         <v>8</v>
       </c>
@@ -3689,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="E131">
-        <f>EXP(3-1.2*(LN(F131)-LN(AVERAGE(F:F)))+0.02*H131)</f>
+        <f t="shared" si="12"/>
         <v>68.625501564847937</v>
       </c>
       <c r="F131">
@@ -3699,11 +5229,23 @@
         <v>0</v>
       </c>
       <c r="H131">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45.1171875</v>
       </c>
-    </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L131">
+        <f t="shared" si="7"/>
+        <v>4.2286642085803692</v>
+      </c>
+      <c r="M131">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N131">
+        <f t="shared" si="9"/>
+        <v>0.13364907659907477</v>
+      </c>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" t="s">
         <v>8</v>
       </c>
@@ -3714,7 +5256,7 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <f>EXP(3-1.2*(LN(F132)-LN(AVERAGE(F:F)))+0.02*H132)</f>
+        <f t="shared" si="12"/>
         <v>322.94832747918548</v>
       </c>
       <c r="F132">
@@ -3724,11 +5266,23 @@
         <v>100</v>
       </c>
       <c r="H132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>122.55859375</v>
       </c>
-    </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L132">
+        <f t="shared" si="7"/>
+        <v>5.7774923335803692</v>
+      </c>
+      <c r="M132">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N132">
+        <f t="shared" si="9"/>
+        <v>1.6824772015990748</v>
+      </c>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" t="s">
         <v>8</v>
       </c>
@@ -3739,7 +5293,7 @@
         <v>25</v>
       </c>
       <c r="E133">
-        <f>EXP(3-1.2*(LN(F133)-LN(AVERAGE(F:F)))+0.02*H133)</f>
+        <f t="shared" si="12"/>
         <v>700.5784816235448</v>
       </c>
       <c r="F133">
@@ -3749,11 +5303,23 @@
         <v>100</v>
       </c>
       <c r="H133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>161.279296875</v>
       </c>
-    </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L133">
+        <f t="shared" si="7"/>
+        <v>6.5519063960803692</v>
+      </c>
+      <c r="M133">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N133">
+        <f t="shared" si="9"/>
+        <v>2.4568912640990748</v>
+      </c>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" t="s">
         <v>8</v>
       </c>
@@ -3764,7 +5330,7 @@
         <v>26</v>
       </c>
       <c r="E134">
-        <f>EXP(3-1.2*(LN(F134)-LN(AVERAGE(F:F)))+0.02*H134)</f>
+        <f t="shared" si="12"/>
         <v>1031.8549948783098</v>
       </c>
       <c r="F134">
@@ -3774,11 +5340,23 @@
         <v>100</v>
       </c>
       <c r="H134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>180.6396484375</v>
       </c>
-    </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L134">
+        <f t="shared" ref="L134:L197" si="15">LN(E134)</f>
+        <v>6.9391134273303692</v>
+      </c>
+      <c r="M134">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N134">
+        <f t="shared" ref="N134:N197" si="16">L134-M134</f>
+        <v>2.8440982953490748</v>
+      </c>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" t="s">
         <v>8</v>
       </c>
@@ -3789,7 +5367,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <f>EXP(3-1.2*(LN(F135)-LN(AVERAGE(F:F)))+0.02*H135)</f>
+        <f t="shared" si="12"/>
         <v>169.47695230195254</v>
       </c>
       <c r="F135">
@@ -3799,11 +5377,23 @@
         <v>0</v>
       </c>
       <c r="H135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>90.31982421875</v>
       </c>
-    </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L135">
+        <f t="shared" si="15"/>
+        <v>5.1327169429553692</v>
+      </c>
+      <c r="M135">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N135">
+        <f t="shared" si="16"/>
+        <v>1.0377018109740748</v>
+      </c>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" t="s">
         <v>8</v>
       </c>
@@ -3814,7 +5404,7 @@
         <v>28</v>
       </c>
       <c r="E136">
-        <f>EXP(3-1.2*(LN(F136)-LN(AVERAGE(F:F)))+0.02*H136)</f>
+        <f t="shared" si="12"/>
         <v>68.684166580627647</v>
       </c>
       <c r="F136">
@@ -3824,11 +5414,23 @@
         <v>0</v>
       </c>
       <c r="H136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45.159912109375</v>
       </c>
-    </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L136">
+        <f t="shared" si="15"/>
+        <v>4.2295187007678692</v>
+      </c>
+      <c r="M136">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N136">
+        <f t="shared" si="16"/>
+        <v>0.13450356878657477</v>
+      </c>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" t="s">
         <v>8</v>
       </c>
@@ -3839,7 +5441,7 @@
         <v>29</v>
       </c>
       <c r="E137">
-        <f>EXP(3-1.2*(LN(F137)-LN(AVERAGE(F:F)))+0.02*H137)</f>
+        <f t="shared" si="12"/>
         <v>323.08633537015089</v>
       </c>
       <c r="F137">
@@ -3849,11 +5451,23 @@
         <v>100</v>
       </c>
       <c r="H137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>122.5799560546875</v>
       </c>
-    </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L137">
+        <f t="shared" si="15"/>
+        <v>5.7779195796741192</v>
+      </c>
+      <c r="M137">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N137">
+        <f t="shared" si="16"/>
+        <v>1.6829044476928248</v>
+      </c>
+    </row>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" t="s">
         <v>8</v>
       </c>
@@ -3864,7 +5478,7 @@
         <v>30</v>
       </c>
       <c r="E138">
-        <f>EXP(3-1.2*(LN(F138)-LN(AVERAGE(F:F)))+0.02*H138)</f>
+        <f t="shared" si="12"/>
         <v>700.7281573198843</v>
       </c>
       <c r="F138">
@@ -3874,11 +5488,23 @@
         <v>100</v>
       </c>
       <c r="H138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>161.28997802734375</v>
       </c>
-    </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L138">
+        <f t="shared" si="15"/>
+        <v>6.5521200191272442</v>
+      </c>
+      <c r="M138">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N138">
+        <f t="shared" si="16"/>
+        <v>2.4571048871459498</v>
+      </c>
+    </row>
+    <row r="139" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +5515,7 @@
         <v>31</v>
       </c>
       <c r="E139">
-        <f>EXP(3-1.2*(LN(F139)-LN(AVERAGE(F:F)))+0.02*H139)</f>
+        <f t="shared" si="12"/>
         <v>634.38885927468186</v>
       </c>
       <c r="F139">
@@ -3899,11 +5525,23 @@
         <v>100</v>
       </c>
       <c r="H139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>180.64498901367188</v>
       </c>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L139">
+        <f t="shared" si="15"/>
+        <v>6.4526621091240104</v>
+      </c>
+      <c r="M139">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N139">
+        <f t="shared" si="16"/>
+        <v>2.357646977142716</v>
+      </c>
+    </row>
+    <row r="140" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" t="s">
         <v>8</v>
       </c>
@@ -3914,7 +5552,7 @@
         <v>32</v>
       </c>
       <c r="E140">
-        <f>EXP(3-1.2*(LN(F140)-LN(AVERAGE(F:F)))+0.02*H140)</f>
+        <f t="shared" si="12"/>
         <v>104.18958986345697</v>
       </c>
       <c r="F140">
@@ -3924,11 +5562,23 @@
         <v>0</v>
       </c>
       <c r="H140">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>90.322494506835938</v>
       </c>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L140">
+        <f t="shared" si="15"/>
+        <v>4.6462122189872916</v>
+      </c>
+      <c r="M140">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N140">
+        <f t="shared" si="16"/>
+        <v>0.55119708700599723</v>
+      </c>
+    </row>
+    <row r="141" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" t="s">
         <v>8</v>
       </c>
@@ -3939,7 +5589,7 @@
         <v>33</v>
       </c>
       <c r="E141">
-        <f>EXP(3-1.2*(LN(F141)-LN(AVERAGE(F:F)))+0.02*H141)</f>
+        <f t="shared" ref="E141:E172" si="17">EXP(3-1.2*(LN(F141)-LN(AVERAGE(F:F)))+0.02*H141)</f>
         <v>42.223936417373743</v>
       </c>
       <c r="F141">
@@ -3949,11 +5599,23 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45.161247253417969</v>
       </c>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L141">
+        <f t="shared" si="15"/>
+        <v>3.7429872739189323</v>
+      </c>
+      <c r="M141">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N141">
+        <f t="shared" si="16"/>
+        <v>-0.35202785806236214</v>
+      </c>
+    </row>
+    <row r="142" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" t="s">
         <v>8</v>
       </c>
@@ -3964,7 +5626,7 @@
         <v>34</v>
       </c>
       <c r="E142">
-        <f>EXP(3-1.2*(LN(F142)-LN(AVERAGE(F:F)))+0.02*H142)</f>
+        <f t="shared" si="17"/>
         <v>198.61629575357523</v>
       </c>
       <c r="F142">
@@ -3974,11 +5636,23 @@
         <v>100</v>
       </c>
       <c r="H142">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>122.58062362670898</v>
       </c>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L142">
+        <f t="shared" si="15"/>
+        <v>5.2913748013847526</v>
+      </c>
+      <c r="M142">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N142">
+        <f t="shared" si="16"/>
+        <v>1.1963596694034582</v>
+      </c>
+    </row>
+    <row r="143" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" t="s">
         <v>8</v>
       </c>
@@ -3989,7 +5663,7 @@
         <v>35</v>
       </c>
       <c r="E143">
-        <f>EXP(3-1.2*(LN(F143)-LN(AVERAGE(F:F)))+0.02*H143)</f>
+        <f t="shared" si="17"/>
         <v>430.76752744901142</v>
       </c>
       <c r="F143">
@@ -3999,11 +5673,23 @@
         <v>100</v>
       </c>
       <c r="H143">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>161.29031181335449</v>
       </c>
-    </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L143">
+        <f t="shared" si="15"/>
+        <v>6.0655685651176627</v>
+      </c>
+      <c r="M143">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N143">
+        <f t="shared" si="16"/>
+        <v>1.9705534331363683</v>
+      </c>
+    </row>
+    <row r="144" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" t="s">
         <v>8</v>
       </c>
@@ -4014,7 +5700,7 @@
         <v>36</v>
       </c>
       <c r="E144">
-        <f>EXP(3-1.2*(LN(F144)-LN(AVERAGE(F:F)))+0.02*H144)</f>
+        <f t="shared" si="17"/>
         <v>634.39097677948178</v>
       </c>
       <c r="F144">
@@ -4024,11 +5710,23 @@
         <v>100</v>
       </c>
       <c r="H144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>180.64515590667725</v>
       </c>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L144">
+        <f t="shared" si="15"/>
+        <v>6.4526654469841178</v>
+      </c>
+      <c r="M144">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N144">
+        <f t="shared" si="16"/>
+        <v>2.3576503150028234</v>
+      </c>
+    </row>
+    <row r="145" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" t="s">
         <v>8</v>
       </c>
@@ -4039,7 +5737,7 @@
         <v>37</v>
       </c>
       <c r="E145">
-        <f>EXP(3-1.2*(LN(F145)-LN(AVERAGE(F:F)))+0.02*H145)</f>
+        <f t="shared" si="17"/>
         <v>104.18976374873988</v>
       </c>
       <c r="F145">
@@ -4049,11 +5747,23 @@
         <v>0</v>
       </c>
       <c r="H145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>90.322577953338623</v>
       </c>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L145">
+        <f t="shared" si="15"/>
+        <v>4.6462138879173454</v>
+      </c>
+      <c r="M145">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N145">
+        <f t="shared" si="16"/>
+        <v>0.55119875593605094</v>
+      </c>
+    </row>
+    <row r="146" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" t="s">
         <v>8</v>
       </c>
@@ -4064,7 +5774,7 @@
         <v>38</v>
       </c>
       <c r="E146">
-        <f>EXP(3-1.2*(LN(F146)-LN(AVERAGE(F:F)))+0.02*H146)</f>
+        <f t="shared" si="17"/>
         <v>42.223971651786684</v>
       </c>
       <c r="F146">
@@ -4074,11 +5784,23 @@
         <v>0</v>
       </c>
       <c r="H146">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45.161288976669312</v>
       </c>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L146">
+        <f t="shared" si="15"/>
+        <v>3.7429881083839591</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N146">
+        <f t="shared" si="16"/>
+        <v>-0.35202702359733529</v>
+      </c>
+    </row>
+    <row r="147" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" t="s">
         <v>8</v>
       </c>
@@ -4089,7 +5811,7 @@
         <v>39</v>
       </c>
       <c r="E147">
-        <f>EXP(3-1.2*(LN(F147)-LN(AVERAGE(F:F)))+0.02*H147)</f>
+        <f t="shared" si="17"/>
         <v>198.61637862276879</v>
       </c>
       <c r="F147">
@@ -4099,11 +5821,23 @@
         <v>100</v>
       </c>
       <c r="H147">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>122.58064448833466</v>
       </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L147">
+        <f t="shared" si="15"/>
+        <v>5.291375218617266</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N147">
+        <f t="shared" si="16"/>
+        <v>1.1963600866359716</v>
+      </c>
+    </row>
+    <row r="148" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" t="s">
         <v>8</v>
       </c>
@@ -4114,7 +5848,7 @@
         <v>40</v>
       </c>
       <c r="E148">
-        <f>EXP(3-1.2*(LN(F148)-LN(AVERAGE(F:F)))+0.02*H148)</f>
+        <f t="shared" si="17"/>
         <v>58.29805749836855</v>
       </c>
       <c r="F148">
@@ -4124,11 +5858,23 @@
         <v>0</v>
       </c>
       <c r="H148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>61.290322244167328</v>
       </c>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L148">
+        <f t="shared" si="15"/>
+        <v>4.0655687737339194</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N148">
+        <f t="shared" si="16"/>
+        <v>-2.944635824737496E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" t="s">
         <v>8</v>
       </c>
@@ -4139,7 +5885,7 @@
         <v>41</v>
       </c>
       <c r="E149">
-        <f>EXP(3-1.2*(LN(F149)-LN(AVERAGE(F:F)))+0.02*H149)</f>
+        <f t="shared" si="17"/>
         <v>31.584470227392849</v>
       </c>
       <c r="F149">
@@ -4149,11 +5895,23 @@
         <v>0</v>
       </c>
       <c r="H149">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>30.645161122083664</v>
       </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L149">
+        <f t="shared" si="15"/>
+        <v>3.4526655512922462</v>
+      </c>
+      <c r="M149">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N149">
+        <f t="shared" si="16"/>
+        <v>-0.64234958068904824</v>
+      </c>
+    </row>
+    <row r="150" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" t="s">
         <v>8</v>
       </c>
@@ -4164,7 +5922,7 @@
         <v>42</v>
       </c>
       <c r="E150">
-        <f>EXP(3-1.2*(LN(F150)-LN(AVERAGE(F:F)))+0.02*H150)</f>
+        <f t="shared" si="17"/>
         <v>23.247879883554788</v>
       </c>
       <c r="F150">
@@ -4174,11 +5932,23 @@
         <v>0</v>
       </c>
       <c r="H150">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>15.322580561041832</v>
       </c>
-    </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L150">
+        <f t="shared" si="15"/>
+        <v>3.1462139400714095</v>
+      </c>
+      <c r="M150">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N150">
+        <f t="shared" si="16"/>
+        <v>-0.94880119190988488</v>
+      </c>
+    </row>
+    <row r="151" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" t="s">
         <v>8</v>
       </c>
@@ -4189,7 +5959,7 @@
         <v>43</v>
       </c>
       <c r="E151">
-        <f>EXP(3-1.2*(LN(F151)-LN(AVERAGE(F:F)))+0.02*H151)</f>
+        <f t="shared" si="17"/>
         <v>19.945192452300219</v>
       </c>
       <c r="F151">
@@ -4199,11 +5969,23 @@
         <v>0</v>
       </c>
       <c r="H151">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>7.661290280520916</v>
       </c>
-    </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L151">
+        <f t="shared" si="15"/>
+        <v>2.9929881344609912</v>
+      </c>
+      <c r="M151">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N151">
+        <f t="shared" si="16"/>
+        <v>-1.1020269975203032</v>
+      </c>
+    </row>
+    <row r="152" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" t="s">
         <v>8</v>
       </c>
@@ -4214,7 +5996,7 @@
         <v>44</v>
       </c>
       <c r="E152">
-        <f>EXP(3-1.2*(LN(F152)-LN(AVERAGE(F:F)))+0.02*H152)</f>
+        <f t="shared" si="17"/>
         <v>18.474201247344752</v>
       </c>
       <c r="F152">
@@ -4224,11 +6006,23 @@
         <v>0</v>
       </c>
       <c r="H152">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>3.830645140260458</v>
       </c>
-    </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L152">
+        <f t="shared" si="15"/>
+        <v>2.9163752316557821</v>
+      </c>
+      <c r="M152">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N152">
+        <f t="shared" si="16"/>
+        <v>-1.1786399003255124</v>
+      </c>
+    </row>
+    <row r="153" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" t="s">
         <v>8</v>
       </c>
@@ -4239,7 +6033,7 @@
         <v>45</v>
       </c>
       <c r="E153">
-        <f>EXP(3-1.2*(LN(F153)-LN(AVERAGE(F:F)))+0.02*H153)</f>
+        <f t="shared" si="17"/>
         <v>17.779903102240748</v>
       </c>
       <c r="F153">
@@ -4249,11 +6043,23 @@
         <v>0</v>
       </c>
       <c r="H153">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>1.915322570130229</v>
       </c>
-    </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L153">
+        <f t="shared" si="15"/>
+        <v>2.8780687802531775</v>
+      </c>
+      <c r="M153">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N153">
+        <f t="shared" si="16"/>
+        <v>-1.2169463517281169</v>
+      </c>
+    </row>
+    <row r="154" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" t="s">
         <v>8</v>
       </c>
@@ -4264,7 +6070,7 @@
         <v>46</v>
       </c>
       <c r="E154">
-        <f>EXP(3-1.2*(LN(F154)-LN(AVERAGE(F:F)))+0.02*H154)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F154">
@@ -4274,11 +6080,23 @@
         <v>0</v>
       </c>
       <c r="H154">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M154">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N154">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="155" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" t="s">
         <v>8</v>
       </c>
@@ -4289,7 +6107,7 @@
         <v>47</v>
       </c>
       <c r="E155">
-        <f>EXP(3-1.2*(LN(F155)-LN(AVERAGE(F:F)))+0.02*H155)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F155">
@@ -4299,11 +6117,23 @@
         <v>0</v>
       </c>
       <c r="H155">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M155">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N155">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="156" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" t="s">
         <v>8</v>
       </c>
@@ -4314,7 +6144,7 @@
         <v>48</v>
       </c>
       <c r="E156">
-        <f>EXP(3-1.2*(LN(F156)-LN(AVERAGE(F:F)))+0.02*H156)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F156">
@@ -4324,11 +6154,23 @@
         <v>0</v>
       </c>
       <c r="H156">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N156">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="157" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" t="s">
         <v>8</v>
       </c>
@@ -4339,7 +6181,7 @@
         <v>49</v>
       </c>
       <c r="E157">
-        <f>EXP(3-1.2*(LN(F157)-LN(AVERAGE(F:F)))+0.02*H157)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F157">
@@ -4349,11 +6191,23 @@
         <v>0</v>
       </c>
       <c r="H157">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M157">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N157">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="158" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" t="s">
         <v>8</v>
       </c>
@@ -4364,7 +6218,7 @@
         <v>50</v>
       </c>
       <c r="E158">
-        <f>EXP(3-1.2*(LN(F158)-LN(AVERAGE(F:F)))+0.02*H158)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F158">
@@ -4374,11 +6228,23 @@
         <v>0</v>
       </c>
       <c r="H158">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M158">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N158">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="159" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" t="s">
         <v>8</v>
       </c>
@@ -4389,7 +6255,7 @@
         <v>51</v>
       </c>
       <c r="E159">
-        <f>EXP(3-1.2*(LN(F159)-LN(AVERAGE(F:F)))+0.02*H159)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F159">
@@ -4399,11 +6265,23 @@
         <v>0</v>
       </c>
       <c r="H159">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N159">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="160" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" t="s">
         <v>8</v>
       </c>
@@ -4414,7 +6292,7 @@
         <v>52</v>
       </c>
       <c r="E160">
-        <f>EXP(3-1.2*(LN(F160)-LN(AVERAGE(F:F)))+0.02*H160)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F160">
@@ -4424,11 +6302,23 @@
         <v>0</v>
       </c>
       <c r="H160">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N160">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="161" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" t="s">
         <v>8</v>
       </c>
@@ -4439,7 +6329,7 @@
         <v>53</v>
       </c>
       <c r="E161">
-        <f>EXP(3-1.2*(LN(F161)-LN(AVERAGE(F:F)))+0.02*H161)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F161">
@@ -4449,11 +6339,23 @@
         <v>0</v>
       </c>
       <c r="H161">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N161">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="162" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" t="s">
         <v>8</v>
       </c>
@@ -4464,7 +6366,7 @@
         <v>54</v>
       </c>
       <c r="E162">
-        <f>EXP(3-1.2*(LN(F162)-LN(AVERAGE(F:F)))+0.02*H162)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F162">
@@ -4474,11 +6376,23 @@
         <v>0</v>
       </c>
       <c r="H162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="163" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" t="s">
         <v>8</v>
       </c>
@@ -4489,7 +6403,7 @@
         <v>55</v>
       </c>
       <c r="E163">
-        <f>EXP(3-1.2*(LN(F163)-LN(AVERAGE(F:F)))+0.02*H163)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F163">
@@ -4499,11 +6413,23 @@
         <v>0</v>
       </c>
       <c r="H163">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="164" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" t="s">
         <v>8</v>
       </c>
@@ -4514,7 +6440,7 @@
         <v>56</v>
       </c>
       <c r="E164">
-        <f>EXP(3-1.2*(LN(F164)-LN(AVERAGE(F:F)))+0.02*H164)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F164">
@@ -4524,11 +6450,23 @@
         <v>0</v>
       </c>
       <c r="H164">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="165" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" t="s">
         <v>8</v>
       </c>
@@ -4539,7 +6477,7 @@
         <v>57</v>
       </c>
       <c r="E165">
-        <f>EXP(3-1.2*(LN(F165)-LN(AVERAGE(F:F)))+0.02*H165)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F165">
@@ -4549,11 +6487,23 @@
         <v>0</v>
       </c>
       <c r="H165">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M165">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N165">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="166" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" t="s">
         <v>8</v>
       </c>
@@ -4564,7 +6514,7 @@
         <v>58</v>
       </c>
       <c r="E166">
-        <f>EXP(3-1.2*(LN(F166)-LN(AVERAGE(F:F)))+0.02*H166)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F166">
@@ -4574,11 +6524,23 @@
         <v>0</v>
       </c>
       <c r="H166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M166">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N166">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="167" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" t="s">
         <v>8</v>
       </c>
@@ -4589,7 +6551,7 @@
         <v>59</v>
       </c>
       <c r="E167">
-        <f>EXP(3-1.2*(LN(F167)-LN(AVERAGE(F:F)))+0.02*H167)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F167">
@@ -4599,11 +6561,23 @@
         <v>0</v>
       </c>
       <c r="H167">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M167">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N167">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="168" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" t="s">
         <v>8</v>
       </c>
@@ -4614,7 +6588,7 @@
         <v>60</v>
       </c>
       <c r="E168">
-        <f>EXP(3-1.2*(LN(F168)-LN(AVERAGE(F:F)))+0.02*H168)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F168">
@@ -4624,11 +6598,23 @@
         <v>0</v>
       </c>
       <c r="H168">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M168">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N168">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="169" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" t="s">
         <v>8</v>
       </c>
@@ -4639,7 +6625,7 @@
         <v>61</v>
       </c>
       <c r="E169">
-        <f>EXP(3-1.2*(LN(F169)-LN(AVERAGE(F:F)))+0.02*H169)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F169">
@@ -4649,11 +6635,23 @@
         <v>0</v>
       </c>
       <c r="H169">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M169">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N169">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="170" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" t="s">
         <v>8</v>
       </c>
@@ -4664,7 +6662,7 @@
         <v>62</v>
       </c>
       <c r="E170">
-        <f>EXP(3-1.2*(LN(F170)-LN(AVERAGE(F:F)))+0.02*H170)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F170">
@@ -4674,11 +6672,23 @@
         <v>0</v>
       </c>
       <c r="H170">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M170">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N170">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="171" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" t="s">
         <v>8</v>
       </c>
@@ -4689,7 +6699,7 @@
         <v>63</v>
       </c>
       <c r="E171">
-        <f>EXP(3-1.2*(LN(F171)-LN(AVERAGE(F:F)))+0.02*H171)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F171">
@@ -4699,11 +6709,23 @@
         <v>0</v>
       </c>
       <c r="H171">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M171">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N171">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="172" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" t="s">
         <v>8</v>
       </c>
@@ -4714,7 +6736,7 @@
         <v>64</v>
       </c>
       <c r="E172">
-        <f>EXP(3-1.2*(LN(F172)-LN(AVERAGE(F:F)))+0.02*H172)</f>
+        <f t="shared" si="17"/>
         <v>17.11169809685309</v>
       </c>
       <c r="F172">
@@ -4724,11 +6746,23 @@
         <v>0</v>
       </c>
       <c r="H172">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M172">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N172">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="173" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" t="s">
         <v>8</v>
       </c>
@@ -4739,7 +6773,7 @@
         <v>65</v>
       </c>
       <c r="E173">
-        <f>EXP(3-1.2*(LN(F173)-LN(AVERAGE(F:F)))+0.02*H173)</f>
+        <f t="shared" ref="E173:E204" si="18">EXP(3-1.2*(LN(F173)-LN(AVERAGE(F:F)))+0.02*H173)</f>
         <v>17.11169809685309</v>
       </c>
       <c r="F173">
@@ -4749,11 +6783,23 @@
         <v>0</v>
       </c>
       <c r="H173">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <f t="shared" si="15"/>
+        <v>2.8397623288505729</v>
+      </c>
+      <c r="M173">
+        <f t="shared" si="13"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N173">
+        <f t="shared" si="16"/>
+        <v>-1.2552528031307215</v>
+      </c>
+    </row>
+    <row r="174" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" t="s">
         <v>8</v>
       </c>
@@ -4764,7 +6810,7 @@
         <v>66</v>
       </c>
       <c r="E174">
-        <f>EXP(3-1.2*(LN(F174)-LN(AVERAGE(F:F)))+0.02*H174)</f>
+        <f t="shared" si="18"/>
         <v>76.689310335591159</v>
       </c>
       <c r="F174">
@@ -4774,11 +6820,23 @@
         <v>75</v>
       </c>
       <c r="H174">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L174">
+        <f t="shared" si="15"/>
+        <v>4.3397623288505729</v>
+      </c>
+      <c r="M174">
+        <f t="shared" ref="M174:M212" si="19">AVERAGE($L$109:$L$212)</f>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N174">
+        <f t="shared" si="16"/>
+        <v>0.24474719686927848</v>
+      </c>
+    </row>
+    <row r="175" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" t="s">
         <v>8</v>
       </c>
@@ -4789,7 +6847,7 @@
         <v>67</v>
       </c>
       <c r="E175">
-        <f>EXP(3-1.2*(LN(F175)-LN(AVERAGE(F:F)))+0.02*H175)</f>
+        <f t="shared" si="18"/>
         <v>162.35127125446104</v>
       </c>
       <c r="F175">
@@ -4799,11 +6857,23 @@
         <v>75</v>
       </c>
       <c r="H175">
-        <f t="shared" ref="H175:H212" si="3">IF(H174*0.5&gt;1,G175+H174*0.5,G175)</f>
+        <f t="shared" ref="H175:H212" si="20">IF(H174*0.5&gt;1,G175+H174*0.5,G175)</f>
         <v>112.5</v>
       </c>
-    </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L175">
+        <f t="shared" si="15"/>
+        <v>5.0897623288505729</v>
+      </c>
+      <c r="M175">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N175">
+        <f t="shared" si="16"/>
+        <v>0.99474719686927848</v>
+      </c>
+    </row>
+    <row r="176" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" t="s">
         <v>8</v>
       </c>
@@ -4814,7 +6884,7 @@
         <v>68</v>
       </c>
       <c r="E176">
-        <f>EXP(3-1.2*(LN(F176)-LN(AVERAGE(F:F)))+0.02*H176)</f>
+        <f t="shared" si="18"/>
         <v>236.21970582759161</v>
       </c>
       <c r="F176">
@@ -4824,11 +6894,23 @@
         <v>75</v>
       </c>
       <c r="H176">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>131.25</v>
       </c>
-    </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L176">
+        <f t="shared" si="15"/>
+        <v>5.4647623288505729</v>
+      </c>
+      <c r="M176">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N176">
+        <f t="shared" si="16"/>
+        <v>1.3697471968692785</v>
+      </c>
+    </row>
+    <row r="177" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" t="s">
         <v>8</v>
       </c>
@@ -4839,7 +6921,7 @@
         <v>69</v>
       </c>
       <c r="E177">
-        <f>EXP(3-1.2*(LN(F177)-LN(AVERAGE(F:F)))+0.02*H177)</f>
+        <f t="shared" si="18"/>
         <v>63.577671321378205</v>
       </c>
       <c r="F177">
@@ -4849,11 +6931,23 @@
         <v>0</v>
       </c>
       <c r="H177">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>65.625</v>
       </c>
-    </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L177">
+        <f t="shared" si="15"/>
+        <v>4.1522623288505729</v>
+      </c>
+      <c r="M177">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N177">
+        <f t="shared" si="16"/>
+        <v>5.7247196869278483E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" t="s">
         <v>8</v>
       </c>
@@ -4864,7 +6958,7 @@
         <v>70</v>
       </c>
       <c r="E178">
-        <f>EXP(3-1.2*(LN(F178)-LN(AVERAGE(F:F)))+0.02*H178)</f>
+        <f t="shared" si="18"/>
         <v>32.983661369720295</v>
       </c>
       <c r="F178">
@@ -4874,11 +6968,23 @@
         <v>0</v>
       </c>
       <c r="H178">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>32.8125</v>
       </c>
-    </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L178">
+        <f t="shared" si="15"/>
+        <v>3.4960123288505729</v>
+      </c>
+      <c r="M178">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N178">
+        <f t="shared" si="16"/>
+        <v>-0.59900280313072152</v>
+      </c>
+    </row>
+    <row r="179" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" t="s">
         <v>8</v>
       </c>
@@ -4889,7 +6995,7 @@
         <v>71</v>
       </c>
       <c r="E179">
-        <f>EXP(3-1.2*(LN(F179)-LN(AVERAGE(F:F)))+0.02*H179)</f>
+        <f t="shared" si="18"/>
         <v>106.47256313895824</v>
       </c>
       <c r="F179">
@@ -4899,11 +7005,23 @@
         <v>75</v>
       </c>
       <c r="H179">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>91.40625</v>
       </c>
-    </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L179">
+        <f t="shared" si="15"/>
+        <v>4.6678873288505729</v>
+      </c>
+      <c r="M179">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N179">
+        <f t="shared" si="16"/>
+        <v>0.57287219686927848</v>
+      </c>
+    </row>
+    <row r="180" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" t="s">
         <v>8</v>
       </c>
@@ -4914,7 +7032,7 @@
         <v>72</v>
       </c>
       <c r="E180">
-        <f>EXP(3-1.2*(LN(F180)-LN(AVERAGE(F:F)))+0.02*H180)</f>
+        <f t="shared" si="18"/>
         <v>191.29654752610969</v>
       </c>
       <c r="F180">
@@ -4924,11 +7042,23 @@
         <v>75</v>
       </c>
       <c r="H180">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>120.703125</v>
       </c>
-    </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L180">
+        <f t="shared" si="15"/>
+        <v>5.2538248288505729</v>
+      </c>
+      <c r="M180">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N180">
+        <f t="shared" si="16"/>
+        <v>1.1588096968692785</v>
+      </c>
+    </row>
+    <row r="181" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" t="s">
         <v>8</v>
       </c>
@@ -4939,7 +7069,7 @@
         <v>73</v>
       </c>
       <c r="E181">
-        <f>EXP(3-1.2*(LN(F181)-LN(AVERAGE(F:F)))+0.02*H181)</f>
+        <f t="shared" si="18"/>
         <v>256.41406490111359</v>
       </c>
       <c r="F181">
@@ -4949,11 +7079,23 @@
         <v>75</v>
       </c>
       <c r="H181">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>135.3515625</v>
       </c>
-    </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L181">
+        <f t="shared" si="15"/>
+        <v>5.5467935788505729</v>
+      </c>
+      <c r="M181">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N181">
+        <f t="shared" si="16"/>
+        <v>1.4517784468692785</v>
+      </c>
+    </row>
+    <row r="182" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" t="s">
         <v>8</v>
       </c>
@@ -4964,7 +7106,7 @@
         <v>74</v>
       </c>
       <c r="E182">
-        <f>EXP(3-1.2*(LN(F182)-LN(AVERAGE(F:F)))+0.02*H182)</f>
+        <f t="shared" si="18"/>
         <v>66.239565716984814</v>
       </c>
       <c r="F182">
@@ -4974,11 +7116,23 @@
         <v>0</v>
       </c>
       <c r="H182">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>67.67578125</v>
       </c>
-    </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L182">
+        <f t="shared" si="15"/>
+        <v>4.1932779538505729</v>
+      </c>
+      <c r="M182">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N182">
+        <f t="shared" si="16"/>
+        <v>9.8262821869278483E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" t="s">
         <v>8</v>
       </c>
@@ -4989,7 +7143,7 @@
         <v>75</v>
       </c>
       <c r="E183">
-        <f>EXP(3-1.2*(LN(F183)-LN(AVERAGE(F:F)))+0.02*H183)</f>
+        <f t="shared" si="18"/>
         <v>33.66706774602897</v>
       </c>
       <c r="F183">
@@ -4999,11 +7153,23 @@
         <v>0</v>
       </c>
       <c r="H183">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>33.837890625</v>
       </c>
-    </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L183">
+        <f t="shared" si="15"/>
+        <v>3.5165201413505729</v>
+      </c>
+      <c r="M183">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N183">
+        <f t="shared" si="16"/>
+        <v>-0.57849499063072152</v>
+      </c>
+    </row>
+    <row r="184" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" t="s">
         <v>8</v>
       </c>
@@ -5014,7 +7180,7 @@
         <v>76</v>
       </c>
       <c r="E184">
-        <f>EXP(3-1.2*(LN(F184)-LN(AVERAGE(F:F)))+0.02*H184)</f>
+        <f t="shared" si="18"/>
         <v>107.56993940117385</v>
       </c>
       <c r="F184">
@@ -5024,11 +7190,23 @@
         <v>75</v>
       </c>
       <c r="H184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>91.9189453125</v>
       </c>
-    </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L184">
+        <f t="shared" si="15"/>
+        <v>4.6781412351005729</v>
+      </c>
+      <c r="M184">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N184">
+        <f t="shared" si="16"/>
+        <v>0.58312610311927848</v>
+      </c>
+    </row>
+    <row r="185" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" t="s">
         <v>8</v>
       </c>
@@ -5039,7 +7217,7 @@
         <v>77</v>
       </c>
       <c r="E185">
-        <f>EXP(3-1.2*(LN(F185)-LN(AVERAGE(F:F)))+0.02*H185)</f>
+        <f t="shared" si="18"/>
         <v>192.27983443734132</v>
       </c>
       <c r="F185">
@@ -5049,11 +7227,23 @@
         <v>75</v>
       </c>
       <c r="H185">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>120.95947265625</v>
       </c>
-    </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L185">
+        <f t="shared" si="15"/>
+        <v>5.2589517819755729</v>
+      </c>
+      <c r="M185">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N185">
+        <f t="shared" si="16"/>
+        <v>1.1639366499942785</v>
+      </c>
+    </row>
+    <row r="186" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" t="s">
         <v>8</v>
       </c>
@@ -5064,7 +7254,7 @@
         <v>78</v>
       </c>
       <c r="E186">
-        <f>EXP(3-1.2*(LN(F186)-LN(AVERAGE(F:F)))+0.02*H186)</f>
+        <f t="shared" si="18"/>
         <v>257.07221956839788</v>
       </c>
       <c r="F186">
@@ -5074,11 +7264,23 @@
         <v>75</v>
       </c>
       <c r="H186">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>135.479736328125</v>
       </c>
-    </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L186">
+        <f t="shared" si="15"/>
+        <v>5.5493570554130729</v>
+      </c>
+      <c r="M186">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N186">
+        <f t="shared" si="16"/>
+        <v>1.4543419234317785</v>
+      </c>
+    </row>
+    <row r="187" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" t="s">
         <v>8</v>
       </c>
@@ -5089,7 +7291,7 @@
         <v>79</v>
       </c>
       <c r="E187">
-        <f>EXP(3-1.2*(LN(F187)-LN(AVERAGE(F:F)))+0.02*H187)</f>
+        <f t="shared" si="18"/>
         <v>66.324521938287305</v>
       </c>
       <c r="F187">
@@ -5099,11 +7301,23 @@
         <v>0</v>
       </c>
       <c r="H187">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>67.7398681640625</v>
       </c>
-    </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L187">
+        <f t="shared" si="15"/>
+        <v>4.1945596921318229</v>
+      </c>
+      <c r="M187">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N187">
+        <f t="shared" si="16"/>
+        <v>9.9544560150528483E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" t="s">
         <v>8</v>
       </c>
@@ -5114,7 +7328,7 @@
         <v>80</v>
       </c>
       <c r="E188">
-        <f>EXP(3-1.2*(LN(F188)-LN(AVERAGE(F:F)))+0.02*H188)</f>
+        <f t="shared" si="18"/>
         <v>33.688650846035408</v>
       </c>
       <c r="F188">
@@ -5124,11 +7338,23 @@
         <v>0</v>
       </c>
       <c r="H188">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>33.86993408203125</v>
       </c>
-    </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L188">
+        <f t="shared" si="15"/>
+        <v>3.5171610104911979</v>
+      </c>
+      <c r="M188">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N188">
+        <f t="shared" si="16"/>
+        <v>-0.57785412149009652</v>
+      </c>
+    </row>
+    <row r="189" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" t="s">
         <v>8</v>
       </c>
@@ -5139,7 +7365,7 @@
         <v>81</v>
       </c>
       <c r="E189">
-        <f>EXP(3-1.2*(LN(F189)-LN(AVERAGE(F:F)))+0.02*H189)</f>
+        <f t="shared" si="18"/>
         <v>107.60441405162433</v>
       </c>
       <c r="F189">
@@ -5149,11 +7375,23 @@
         <v>75</v>
       </c>
       <c r="H189">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>91.934967041015625</v>
       </c>
-    </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L189">
+        <f t="shared" si="15"/>
+        <v>4.6784616696708854</v>
+      </c>
+      <c r="M189">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N189">
+        <f t="shared" si="16"/>
+        <v>0.58344653768959098</v>
+      </c>
+    </row>
+    <row r="190" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" t="s">
         <v>8</v>
       </c>
@@ -5164,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="E190">
-        <f>EXP(3-1.2*(LN(F190)-LN(AVERAGE(F:F)))+0.02*H190)</f>
+        <f t="shared" si="18"/>
         <v>192.31064345840809</v>
       </c>
       <c r="F190">
@@ -5174,11 +7412,23 @@
         <v>75</v>
       </c>
       <c r="H190">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>120.96748352050781</v>
       </c>
-    </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L190">
+        <f t="shared" si="15"/>
+        <v>5.2591119992607291</v>
+      </c>
+      <c r="M190">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N190">
+        <f t="shared" si="16"/>
+        <v>1.1640968672794347</v>
+      </c>
+    </row>
+    <row r="191" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" t="s">
         <v>8</v>
       </c>
@@ -5189,7 +7439,7 @@
         <v>83</v>
       </c>
       <c r="E191">
-        <f>EXP(3-1.2*(LN(F191)-LN(AVERAGE(F:F)))+0.02*H191)</f>
+        <f t="shared" si="18"/>
         <v>257.09281409984106</v>
       </c>
       <c r="F191">
@@ -5199,11 +7449,23 @@
         <v>75</v>
       </c>
       <c r="H191">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>135.48374176025391</v>
       </c>
-    </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L191">
+        <f t="shared" si="15"/>
+        <v>5.549437164055651</v>
+      </c>
+      <c r="M191">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N191">
+        <f t="shared" si="16"/>
+        <v>1.4544220320743566</v>
+      </c>
+    </row>
+    <row r="192" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" t="s">
         <v>8</v>
       </c>
@@ -5214,7 +7476,7 @@
         <v>84</v>
       </c>
       <c r="E192">
-        <f>EXP(3-1.2*(LN(F192)-LN(AVERAGE(F:F)))+0.02*H192)</f>
+        <f t="shared" si="18"/>
         <v>66.327178575202907</v>
       </c>
       <c r="F192">
@@ -5224,11 +7486,23 @@
         <v>0</v>
       </c>
       <c r="H192">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>67.741870880126953</v>
       </c>
-    </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L192">
+        <f t="shared" si="15"/>
+        <v>4.194599746453112</v>
+      </c>
+      <c r="M192">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N192">
+        <f t="shared" si="16"/>
+        <v>9.9584614471817545E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" t="s">
         <v>8</v>
       </c>
@@ -5239,7 +7513,7 @@
         <v>85</v>
       </c>
       <c r="E193">
-        <f>EXP(3-1.2*(LN(F193)-LN(AVERAGE(F:F)))+0.02*H193)</f>
+        <f t="shared" si="18"/>
         <v>33.689325540813883</v>
       </c>
       <c r="F193">
@@ -5249,11 +7523,23 @@
         <v>0</v>
       </c>
       <c r="H193">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>33.870935440063477</v>
       </c>
-    </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L193">
+        <f t="shared" si="15"/>
+        <v>3.5171810376518424</v>
+      </c>
+      <c r="M193">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N193">
+        <f t="shared" si="16"/>
+        <v>-0.57783409432945199</v>
+      </c>
+    </row>
+    <row r="194" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" t="s">
         <v>8</v>
       </c>
@@ -5264,7 +7550,7 @@
         <v>86</v>
       </c>
       <c r="E194">
-        <f>EXP(3-1.2*(LN(F194)-LN(AVERAGE(F:F)))+0.02*H194)</f>
+        <f t="shared" si="18"/>
         <v>107.60549156246233</v>
       </c>
       <c r="F194">
@@ -5274,11 +7560,23 @@
         <v>75</v>
       </c>
       <c r="H194">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>91.935467720031738</v>
       </c>
-    </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L194">
+        <f t="shared" si="15"/>
+        <v>4.6784716832512077</v>
+      </c>
+      <c r="M194">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N194">
+        <f t="shared" si="16"/>
+        <v>0.58345655126991325</v>
+      </c>
+    </row>
+    <row r="195" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B195" t="s">
         <v>8</v>
       </c>
@@ -5289,7 +7587,7 @@
         <v>87</v>
       </c>
       <c r="E195">
-        <f>EXP(3-1.2*(LN(F195)-LN(AVERAGE(F:F)))+0.02*H195)</f>
+        <f t="shared" si="18"/>
         <v>192.31160631985608</v>
       </c>
       <c r="F195">
@@ -5299,11 +7597,23 @@
         <v>75</v>
       </c>
       <c r="H195">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>120.96773386001587</v>
       </c>
-    </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L195">
+        <f t="shared" si="15"/>
+        <v>5.2591170060508903</v>
+      </c>
+      <c r="M195">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N195">
+        <f t="shared" si="16"/>
+        <v>1.1641018740695959</v>
+      </c>
+    </row>
+    <row r="196" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B196" t="s">
         <v>8</v>
       </c>
@@ -5314,7 +7624,7 @@
         <v>88</v>
       </c>
       <c r="E196">
-        <f>EXP(3-1.2*(LN(F196)-LN(AVERAGE(F:F)))+0.02*H196)</f>
+        <f t="shared" si="18"/>
         <v>257.09345770553273</v>
       </c>
       <c r="F196">
@@ -5324,11 +7634,23 @@
         <v>75</v>
       </c>
       <c r="H196">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>135.48386693000793</v>
       </c>
-    </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L196">
+        <f t="shared" si="15"/>
+        <v>5.5494396674507316</v>
+      </c>
+      <c r="M196">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N196">
+        <f t="shared" si="16"/>
+        <v>1.4544245354694372</v>
+      </c>
+    </row>
+    <row r="197" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B197" t="s">
         <v>8</v>
       </c>
@@ -5339,7 +7661,7 @@
         <v>89</v>
       </c>
       <c r="E197">
-        <f>EXP(3-1.2*(LN(F197)-LN(AVERAGE(F:F)))+0.02*H197)</f>
+        <f t="shared" si="18"/>
         <v>66.327261596821145</v>
       </c>
       <c r="F197">
@@ -5349,11 +7671,23 @@
         <v>0</v>
       </c>
       <c r="H197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>67.741933465003967</v>
       </c>
-    </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L197">
+        <f t="shared" si="15"/>
+        <v>4.1946009981506522</v>
+      </c>
+      <c r="M197">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N197">
+        <f t="shared" si="16"/>
+        <v>9.9585866169357828E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B198" t="s">
         <v>8</v>
       </c>
@@ -5364,7 +7698,7 @@
         <v>90</v>
       </c>
       <c r="E198">
-        <f>EXP(3-1.2*(LN(F198)-LN(AVERAGE(F:F)))+0.02*H198)</f>
+        <f t="shared" si="18"/>
         <v>44.033641665389823</v>
       </c>
       <c r="F198">
@@ -5374,11 +7708,23 @@
         <v>0</v>
       </c>
       <c r="H198">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>33.870966732501984</v>
       </c>
-    </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L198">
+        <f t="shared" ref="L198:L212" si="21">LN(E198)</f>
+        <v>3.784953925077664</v>
+      </c>
+      <c r="M198">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N198">
+        <f t="shared" ref="N198:N212" si="22">L198-M198</f>
+        <v>-0.31006120690363037</v>
+      </c>
+    </row>
+    <row r="199" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B199" t="s">
         <v>8</v>
       </c>
@@ -5389,7 +7735,7 @@
         <v>91</v>
       </c>
       <c r="E199">
-        <f>EXP(3-1.2*(LN(F199)-LN(AVERAGE(F:F)))+0.02*H199)</f>
+        <f t="shared" si="18"/>
         <v>140.64574157864669</v>
       </c>
       <c r="F199">
@@ -5399,11 +7745,23 @@
         <v>75</v>
       </c>
       <c r="H199">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>91.935483366250992</v>
       </c>
-    </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L199">
+        <f t="shared" si="21"/>
+        <v>4.9462442577526442</v>
+      </c>
+      <c r="M199">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N199">
+        <f t="shared" si="22"/>
+        <v>0.85122912577134979</v>
+      </c>
+    </row>
+    <row r="200" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" t="s">
         <v>8</v>
       </c>
@@ -5414,7 +7772,7 @@
         <v>92</v>
       </c>
       <c r="E200">
-        <f>EXP(3-1.2*(LN(F200)-LN(AVERAGE(F:F)))+0.02*H200)</f>
+        <f t="shared" si="18"/>
         <v>56.086179311298103</v>
       </c>
       <c r="F200">
@@ -5424,11 +7782,23 @@
         <v>0</v>
       </c>
       <c r="H200">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>45.967741683125496</v>
       </c>
-    </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L200">
+        <f t="shared" si="21"/>
+        <v>4.0268894240901343</v>
+      </c>
+      <c r="M200">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N200">
+        <f t="shared" si="22"/>
+        <v>-6.8125707891160125E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B201" t="s">
         <v>8</v>
       </c>
@@ -5439,7 +7809,7 @@
         <v>93</v>
       </c>
       <c r="E201">
-        <f>EXP(3-1.2*(LN(F201)-LN(AVERAGE(F:F)))+0.02*H201)</f>
+        <f t="shared" si="18"/>
         <v>35.417711053068977</v>
       </c>
       <c r="F201">
@@ -5449,11 +7819,23 @@
         <v>0</v>
       </c>
       <c r="H201">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>22.983870841562748</v>
       </c>
-    </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L201">
+        <f t="shared" si="21"/>
+        <v>3.5672120072588793</v>
+      </c>
+      <c r="M201">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N201">
+        <f t="shared" si="22"/>
+        <v>-0.52780312472241508</v>
+      </c>
+    </row>
+    <row r="202" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" t="s">
         <v>8</v>
       </c>
@@ -5464,7 +7846,7 @@
         <v>94</v>
       </c>
       <c r="E202">
-        <f>EXP(3-1.2*(LN(F202)-LN(AVERAGE(F:F)))+0.02*H202)</f>
+        <f t="shared" si="18"/>
         <v>28.145100757233138</v>
       </c>
       <c r="F202">
@@ -5474,11 +7856,23 @@
         <v>0</v>
       </c>
       <c r="H202">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>11.491935420781374</v>
       </c>
-    </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L202">
+        <f t="shared" si="21"/>
+        <v>3.3373732988432518</v>
+      </c>
+      <c r="M202">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N202">
+        <f t="shared" si="22"/>
+        <v>-0.75764183313804256</v>
+      </c>
+    </row>
+    <row r="203" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" t="s">
         <v>8</v>
       </c>
@@ -5489,7 +7883,7 @@
         <v>95</v>
       </c>
       <c r="E203">
-        <f>EXP(3-1.2*(LN(F203)-LN(AVERAGE(F:F)))+0.02*H203)</f>
+        <f t="shared" si="18"/>
         <v>25.089613221992064</v>
       </c>
       <c r="F203">
@@ -5499,11 +7893,23 @@
         <v>0</v>
       </c>
       <c r="H203">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>5.745967710390687</v>
       </c>
-    </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L203">
+        <f t="shared" si="21"/>
+        <v>3.2224539446354381</v>
+      </c>
+      <c r="M203">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N203">
+        <f t="shared" si="22"/>
+        <v>-0.8725611873458563</v>
+      </c>
+    </row>
+    <row r="204" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" t="s">
         <v>8</v>
       </c>
@@ -5514,7 +7920,7 @@
         <v>96</v>
       </c>
       <c r="E204">
-        <f>EXP(3-1.2*(LN(F204)-LN(AVERAGE(F:F)))+0.02*H204)</f>
+        <f t="shared" si="18"/>
         <v>23.688608238242079</v>
       </c>
       <c r="F204">
@@ -5524,11 +7930,23 @@
         <v>0</v>
       </c>
       <c r="H204">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>2.8729838551953435</v>
       </c>
-    </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L204">
+        <f t="shared" si="21"/>
+        <v>3.1649942675315312</v>
+      </c>
+      <c r="M204">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N204">
+        <f t="shared" si="22"/>
+        <v>-0.93002086444976317</v>
+      </c>
+    </row>
+    <row r="205" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" t="s">
         <v>8</v>
       </c>
@@ -5539,7 +7957,7 @@
         <v>97</v>
       </c>
       <c r="E205">
-        <f>EXP(3-1.2*(LN(F205)-LN(AVERAGE(F:F)))+0.02*H205)</f>
+        <f t="shared" ref="E205:E236" si="23">EXP(3-1.2*(LN(F205)-LN(AVERAGE(F:F)))+0.02*H205)</f>
         <v>23.017721724035326</v>
       </c>
       <c r="F205">
@@ -5549,11 +7967,23 @@
         <v>0</v>
       </c>
       <c r="H205">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>1.4364919275976717</v>
       </c>
-    </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="L205">
+        <f t="shared" si="21"/>
+        <v>3.1362644289795778</v>
+      </c>
+      <c r="M205">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N205">
+        <f t="shared" si="22"/>
+        <v>-0.95875070300171661</v>
+      </c>
+    </row>
+    <row r="206" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" t="s">
         <v>8</v>
       </c>
@@ -5564,7 +7994,7 @@
         <v>98</v>
       </c>
       <c r="E206">
-        <f>EXP(3-1.2*(LN(F206)-LN(AVERAGE(F:F)))+0.02*H206)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F206">
@@ -5574,11 +8004,23 @@
         <v>0</v>
       </c>
       <c r="H206">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M206">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N206">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="207" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" t="s">
         <v>8</v>
       </c>
@@ -5589,7 +8031,7 @@
         <v>99</v>
       </c>
       <c r="E207">
-        <f>EXP(3-1.2*(LN(F207)-LN(AVERAGE(F:F)))+0.02*H207)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F207">
@@ -5599,11 +8041,23 @@
         <v>0</v>
       </c>
       <c r="H207">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M207">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N207">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="208" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B208" t="s">
         <v>8</v>
       </c>
@@ -5614,7 +8068,7 @@
         <v>100</v>
       </c>
       <c r="E208">
-        <f>EXP(3-1.2*(LN(F208)-LN(AVERAGE(F:F)))+0.02*H208)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F208">
@@ -5624,11 +8078,23 @@
         <v>0</v>
       </c>
       <c r="H208">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M208">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N208">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="209" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B209" t="s">
         <v>8</v>
       </c>
@@ -5639,7 +8105,7 @@
         <v>101</v>
       </c>
       <c r="E209">
-        <f>EXP(3-1.2*(LN(F209)-LN(AVERAGE(F:F)))+0.02*H209)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F209">
@@ -5649,11 +8115,23 @@
         <v>0</v>
       </c>
       <c r="H209">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M209">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N209">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="210" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B210" t="s">
         <v>8</v>
       </c>
@@ -5664,7 +8142,7 @@
         <v>102</v>
       </c>
       <c r="E210">
-        <f>EXP(3-1.2*(LN(F210)-LN(AVERAGE(F:F)))+0.02*H210)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F210">
@@ -5674,11 +8152,23 @@
         <v>0</v>
       </c>
       <c r="H210">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M210">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N210">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="211" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B211" t="s">
         <v>8</v>
       </c>
@@ -5689,7 +8179,7 @@
         <v>103</v>
       </c>
       <c r="E211">
-        <f>EXP(3-1.2*(LN(F211)-LN(AVERAGE(F:F)))+0.02*H211)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F211">
@@ -5699,11 +8189,23 @@
         <v>0</v>
       </c>
       <c r="H211">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M211">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N211">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
+      </c>
+    </row>
+    <row r="212" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" t="s">
         <v>8</v>
       </c>
@@ -5714,7 +8216,7 @@
         <v>104</v>
       </c>
       <c r="E212">
-        <f>EXP(3-1.2*(LN(F212)-LN(AVERAGE(F:F)))+0.02*H212)</f>
+        <f t="shared" si="23"/>
         <v>22.365835427588003</v>
       </c>
       <c r="F212">
@@ -5724,8 +8226,20 @@
         <v>0</v>
       </c>
       <c r="H212">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <f t="shared" si="21"/>
+        <v>3.1075345904276244</v>
+      </c>
+      <c r="M212">
+        <f t="shared" si="19"/>
+        <v>4.0950151319812944</v>
+      </c>
+      <c r="N212">
+        <f t="shared" si="22"/>
+        <v>-0.98748054155367004</v>
       </c>
     </row>
   </sheetData>

--- a/static/downloads/Input Template -- File name will be analysis title.xlsx
+++ b/static/downloads/Input Template -- File name will be analysis title.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeamLorenzen\Documents\App0\static\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B1A27305-03F2-47EF-B15D-8A1C80CDDA98}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{7C8FD631-6B04-4634-97A1-C9991BCC2504}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="6852" windowHeight="4692" xr2:uid="{A1AE285A-40C5-42A2-B68C-1B9EC99F826A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="6852" windowHeight="4692" activeTab="1" xr2:uid="{A1AE285A-40C5-42A2-B68C-1B9EC99F826A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="32">
   <si>
     <t>gid</t>
   </si>
@@ -107,12 +108,31 @@
   <si>
     <t>log y -mean log y</t>
   </si>
+  <si>
+    <t>TV1</t>
+  </si>
+  <si>
+    <t>TV2</t>
+  </si>
+  <si>
+    <t>ProgVideo1</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>adstock</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="0.00000000"/>
+    <numFmt numFmtId="167" formatCode="0.000000000000000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,13 +140,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="4"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5FE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -141,8 +173,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,13 +494,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE90F50-471E-417F-9EB4-10FF26C6D164}">
-  <dimension ref="A1:N212"/>
+  <dimension ref="A1:S212"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="23.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -489,7 +526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -512,7 +549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -526,7 +563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -536,6 +573,13 @@
       <c r="G4" t="s">
         <v>10</v>
       </c>
+      <c r="I4" s="1">
+        <v>14.340949</v>
+      </c>
+      <c r="J4" s="1">
+        <v>-4.1007559999999996</v>
+      </c>
+      <c r="K4" s="1"/>
       <c r="L4" t="s">
         <v>24</v>
       </c>
@@ -546,7 +590,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -557,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E36" si="0">EXP(2-1.2*(LN(F5)-LN(AVERAGE(F:F)))+0.02*H5)</f>
+        <f>EXP(2-1.2*(LN(F5)-LN(AVERAGE(F:F)))+0.02*H5)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F5">
@@ -583,7 +627,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -594,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E6:E36" si="0">EXP(2-1.2*(LN(F6)-LN(AVERAGE(F:F)))+0.02*H6)</f>
         <v>10.240192912859774</v>
       </c>
       <c r="F6">
@@ -620,7 +664,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -657,7 +701,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -693,8 +737,12 @@
         <f t="shared" si="3"/>
         <v>-0.76869467340092967</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -731,7 +779,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -768,7 +816,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>6</v>
       </c>
@@ -805,7 +853,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -842,7 +890,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>6</v>
       </c>
@@ -879,7 +927,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>6</v>
       </c>
@@ -916,7 +964,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
         <v>6</v>
       </c>
@@ -953,7 +1001,7 @@
         <v>-0.76869467340092967</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>6</v>
       </c>
@@ -4109,7 +4157,7 @@
         <v>97</v>
       </c>
       <c r="E101">
-        <f t="shared" ref="E101:E132" si="11">EXP(2-1.2*(LN(F101)-LN(AVERAGE(F:F)))+0.02*H101)</f>
+        <f t="shared" ref="E101:E108" si="11">EXP(2-1.2*(LN(F101)-LN(AVERAGE(F:F)))+0.02*H101)</f>
         <v>8.4677466048778829</v>
       </c>
       <c r="F101">
@@ -7957,7 +8005,7 @@
         <v>97</v>
       </c>
       <c r="E205">
-        <f t="shared" ref="E205:E236" si="23">EXP(3-1.2*(LN(F205)-LN(AVERAGE(F:F)))+0.02*H205)</f>
+        <f t="shared" ref="E205:E212" si="23">EXP(3-1.2*(LN(F205)-LN(AVERAGE(F:F)))+0.02*H205)</f>
         <v>23.017721724035326</v>
       </c>
       <c r="F205">
@@ -8240,6 +8288,9111 @@
       <c r="N212">
         <f t="shared" si="22"/>
         <v>-0.98748054155367004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CBFD49-6547-4AFC-AF47-8D7082EE096B}">
+  <dimension ref="A1:N212"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="13" max="13" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.83984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>EXP(2-1.2*(LN(E5)-LN(AVERAGE(E:E)))+0.02*I5+0.025*J5+0.03*K5)</f>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>F5</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>G5</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>H5</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="2">
+        <f>LN(D5)</f>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N5" s="3">
+        <f>M5-AVERAGE($M$5:$M$108)</f>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D69" si="0">EXP(2-1.2*(LN(E6)-LN(AVERAGE(E:E)))+0.02*I6+0.025*J6+0.03*K6)</f>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>I5*0.5+F6</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>J5*0.5+G6</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>K5*0.5+H6</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" ref="M6:M69" si="1">LN(D6)</f>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" ref="N6:N69" si="2">M6-AVERAGE($M$5:$M$108)</f>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f t="shared" ref="I7:K70" si="3">I6*0.5+F7</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>11</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>14</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>15</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3263204585803696</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.69625963229635701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>75.665359896992911</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3263204585803692</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3037403677036425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>205.67977285180959</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3263204585803692</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3037403677036425</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <f>EXP(2-1.2*(LN(E20)-LN(AVERAGE(E:E)))+0.02*I20+0.025*J20+0.03*K20)</f>
+        <v>339.10861645354925</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="1"/>
+        <v>5.8263204585803692</v>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="2"/>
+        <v>2.8037403677036425</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>17</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>58.928241539157753</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>87.5</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="1"/>
+        <v>4.0763204585803692</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0537403677036425</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>24.564945784116286</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>43.75</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="1"/>
+        <v>3.2013204585803696</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="2"/>
+        <v>0.17874036770364299</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>15.860321047295738</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>21.875</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7638204585803696</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.25875963229635701</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>12.744125987457851</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>10.9375</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5450704585803696</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.47750963229635701</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>21</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>11.423760703785684</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>5.46875</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4356954585803696</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.58688463229635701</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>22</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>10.815799249112946</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="3"/>
+        <v>2.734375</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3810079585803696</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.64157213229635701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>10.524061517193847</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>1.3671875</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3536642085803696</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.66891588229635701</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>76.706951268364378</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>100.68359375</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3399923335803692</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3174122427036425</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>207.09060360545556</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>150.341796875</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3331563960803692</v>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3105763052036425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>340.26966218613165</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>175.1708984375</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="1"/>
+        <v>5.8297384273303692</v>
+      </c>
+      <c r="N30" s="3">
+        <f t="shared" si="2"/>
+        <v>2.8071583364536425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>27</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>59.029035085960992</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>87.58544921875</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <f t="shared" si="1"/>
+        <v>4.0780294429553692</v>
+      </c>
+      <c r="N31" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0554493520786425</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>28</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>24.585945309062431</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>43.792724609375</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <f t="shared" si="1"/>
+        <v>3.2021749507678696</v>
+      </c>
+      <c r="N32" s="3">
+        <f t="shared" si="2"/>
+        <v>0.17959485989114299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>15.867098755280347</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>21.8963623046875</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7642477046741196</v>
+      </c>
+      <c r="N33" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.25833238620260701</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>12.746848717289618</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="3"/>
+        <v>10.94818115234375</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5452840816272446</v>
+      </c>
+      <c r="N34" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.47729600924948201</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>31</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>7.0233768867458046</v>
+      </c>
+      <c r="E35">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="3"/>
+        <v>5.474090576171875</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9492441403740102</v>
+      </c>
+      <c r="N35" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.0733359505027165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>32</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>6.6492444695536337</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="3"/>
+        <v>2.7370452880859375</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8945032346122914</v>
+      </c>
+      <c r="N36" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1280768562644352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>33</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>6.4697196817971765</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="3"/>
+        <v>1.3685226440429688</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="1"/>
+        <v>1.867132781731432</v>
+      </c>
+      <c r="N37" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1554473091452946</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>34</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>47.155354007831825</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="3"/>
+        <v>100.68426132202148</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="1"/>
+        <v>3.8534475552910026</v>
+      </c>
+      <c r="N38" s="3">
+        <f t="shared" si="2"/>
+        <v>0.83086746441427595</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>35</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>127.30743918475332</v>
+      </c>
+      <c r="E39">
+        <v>15</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="3"/>
+        <v>150.34213066101074</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <f t="shared" si="1"/>
+        <v>4.8466049420707877</v>
+      </c>
+      <c r="N39" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8240248511940611</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>209.17759656375449</v>
+      </c>
+      <c r="E40">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="3"/>
+        <v>175.17106533050537</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3431836354606803</v>
+      </c>
+      <c r="N40" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3206035445839537</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>37</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>36.287487401159211</v>
+      </c>
+      <c r="E41">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="3"/>
+        <v>87.585532665252686</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <f t="shared" si="1"/>
+        <v>3.5914729821556266</v>
+      </c>
+      <c r="N41" s="3">
+        <f t="shared" si="2"/>
+        <v>0.56889289127889997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>38</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>15.113942399213457</v>
+      </c>
+      <c r="E42">
+        <v>15</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="3"/>
+        <v>43.792766332626343</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7156176555030997</v>
+      </c>
+      <c r="N42" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.30696243537362689</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>39</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>9.7541222660733613</v>
+      </c>
+      <c r="E43">
+        <v>15</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="3"/>
+        <v>21.896383166313171</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="2">
+        <f t="shared" si="1"/>
+        <v>2.2776899921768363</v>
+      </c>
+      <c r="N43" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.74489009869989031</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>40</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>10.577468869422685</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="3"/>
+        <v>10.948191583156586</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="M44" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3587261605137044</v>
+      </c>
+      <c r="N44" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.6638539303630222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>41</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>11.014848703711642</v>
+      </c>
+      <c r="E45">
+        <v>15</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="3"/>
+        <v>5.4740957915782928</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="M45" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3992442446821385</v>
+      </c>
+      <c r="N45" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.62333584619458815</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>42</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>11.240274734818675</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="3"/>
+        <v>2.7370478957891464</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="3"/>
+        <v>17.5</v>
+      </c>
+      <c r="M46" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4195032867663557</v>
+      </c>
+      <c r="N46" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.6030768041103709</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>43</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>11.354711952863022</v>
+      </c>
+      <c r="E47">
+        <v>15</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>10</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="3"/>
+        <v>1.3685239478945732</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="3"/>
+        <v>18.75</v>
+      </c>
+      <c r="M47" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4296328078084644</v>
+      </c>
+      <c r="N47" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.59294728306826228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>44</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>11.412366730264361</v>
+      </c>
+      <c r="E48">
+        <v>15</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="3"/>
+        <v>0.68426197394728661</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="3"/>
+        <v>19.375</v>
+      </c>
+      <c r="M48" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4346975683295184</v>
+      </c>
+      <c r="N48" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.58788252254720819</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>45</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>11.441303806874448</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="3"/>
+        <v>0.3421309869736433</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="3"/>
+        <v>19.6875</v>
+      </c>
+      <c r="M49" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4372299485900455</v>
+      </c>
+      <c r="N49" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.58535014228668114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>46</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>11.455799848267615</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="3"/>
+        <v>0.17106549348682165</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="3"/>
+        <v>19.84375</v>
+      </c>
+      <c r="M50" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4384961387203092</v>
+      </c>
+      <c r="N50" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.5840839521564174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>47</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>11.463054754899165</v>
+      </c>
+      <c r="E51">
+        <v>15</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>10</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="3"/>
+        <v>8.5532746743410826E-2</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="3"/>
+        <v>19.921875</v>
+      </c>
+      <c r="M51" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4391292337854411</v>
+      </c>
+      <c r="N51" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.58345085709128552</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52">
+        <v>48</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>15.478404297910828</v>
+      </c>
+      <c r="E52">
+        <v>15</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>20</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="3"/>
+        <v>4.2766373371705413E-2</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="3"/>
+        <v>29.9609375</v>
+      </c>
+      <c r="M52" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7394457813180066</v>
+      </c>
+      <c r="N52" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.28313430955871999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53">
+        <v>49</v>
+      </c>
+      <c r="D53">
+        <f>EXP(2-1.2*(LN(E53)-LN(AVERAGE(E:E)))+0.02*I53+0.025*J53+0.03*K53)</f>
+        <v>13.324494792634002</v>
+      </c>
+      <c r="E53">
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>10</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="3"/>
+        <v>2.1383186685852706E-2</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="3"/>
+        <v>24.98046875</v>
+      </c>
+      <c r="M53" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5896040550842896</v>
+      </c>
+      <c r="N53" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.43297603579243704</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>50</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>12.362691558651548</v>
+      </c>
+      <c r="E54">
+        <v>15</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>10</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="3"/>
+        <v>1.0691593342926353E-2</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="3"/>
+        <v>22.490234375</v>
+      </c>
+      <c r="M54" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5146831919674311</v>
+      </c>
+      <c r="N54" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.50789689890929557</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55">
+        <v>51</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>11.908146674781472</v>
+      </c>
+      <c r="E55">
+        <v>15</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>10</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="3"/>
+        <v>5.3457966714631766E-3</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="3"/>
+        <v>21.2451171875</v>
+      </c>
+      <c r="M55" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4772227604090018</v>
+      </c>
+      <c r="N55" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.54535733046772483</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56">
+        <v>52</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>11.687180351421311</v>
+      </c>
+      <c r="E56">
+        <v>15</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="3"/>
+        <v>2.6728983357315883E-3</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="3"/>
+        <v>20.62255859375</v>
+      </c>
+      <c r="M56" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4584925446297872</v>
+      </c>
+      <c r="N56" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.56408754624693946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>53</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>8.5773708323118285</v>
+      </c>
+      <c r="E57">
+        <v>15</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="3"/>
+        <v>1.3364491678657942E-3</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="3"/>
+        <v>10.311279296875</v>
+      </c>
+      <c r="M57" s="2">
+        <f t="shared" si="1"/>
+        <v>2.14912743674018</v>
+      </c>
+      <c r="N57" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.8734526541365466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>54</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>7.3481228260980114</v>
+      </c>
+      <c r="E58">
+        <v>15</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="3"/>
+        <v>6.6822458393289708E-4</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="3"/>
+        <v>5.1556396484375</v>
+      </c>
+      <c r="M58" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9944448827953762</v>
+      </c>
+      <c r="N58" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.0281352080813504</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>55</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>6.8012308681445051</v>
+      </c>
+      <c r="E59">
+        <v>15</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="3"/>
+        <v>3.3411229196644854E-4</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="3"/>
+        <v>2.57781982421875</v>
+      </c>
+      <c r="M59" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9171036058229745</v>
+      </c>
+      <c r="N59" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1054764850537522</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>56</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>6.5432433481771399</v>
+      </c>
+      <c r="E60">
+        <v>15</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="3"/>
+        <v>1.6705614598322427E-4</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="3"/>
+        <v>1.288909912109375</v>
+      </c>
+      <c r="M60" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8784329673367737</v>
+      </c>
+      <c r="N60" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.144147123539953</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61">
+        <v>57</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>6.4179429147496352</v>
+      </c>
+      <c r="E61">
+        <v>15</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="3"/>
+        <v>8.3528072991612135E-5</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="3"/>
+        <v>0.6444549560546875</v>
+      </c>
+      <c r="M61" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8590976480936732</v>
+      </c>
+      <c r="N61" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1634824427830535</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62">
+        <v>58</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>6.3561953851569193</v>
+      </c>
+      <c r="E62">
+        <v>15</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="3"/>
+        <v>4.1764036495806067E-5</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="3"/>
+        <v>0.32222747802734375</v>
+      </c>
+      <c r="M62" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8494299884721228</v>
+      </c>
+      <c r="N62" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1731501024046038</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>59</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>6.325544758060154</v>
+      </c>
+      <c r="E63">
+        <v>15</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="3"/>
+        <v>2.0882018247903034E-5</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="3"/>
+        <v>0.16111373901367188</v>
+      </c>
+      <c r="M63" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8445961586613477</v>
+      </c>
+      <c r="N63" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1779839322153789</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>60</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>6.3102749150385069</v>
+      </c>
+      <c r="E64">
+        <v>15</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="3"/>
+        <v>1.0441009123951517E-5</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="3"/>
+        <v>8.0556869506835938E-2</v>
+      </c>
+      <c r="M64" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8421792437559603</v>
+      </c>
+      <c r="N64" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1804008471207663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>61</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>6.3026538220996295</v>
+      </c>
+      <c r="E65">
+        <v>15</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="3"/>
+        <v>5.2205045619757584E-6</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="3"/>
+        <v>4.0278434753417969E-2</v>
+      </c>
+      <c r="M65" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8409707863032665</v>
+      </c>
+      <c r="N65" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1816093045734601</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>62</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>6.2988467279017639</v>
+      </c>
+      <c r="E66">
+        <v>15</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="3"/>
+        <v>2.6102522809878792E-6</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="3"/>
+        <v>2.0139217376708984E-2</v>
+      </c>
+      <c r="M66" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8403665575769195</v>
+      </c>
+      <c r="N66" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1822135332998072</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>63</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="0"/>
+        <v>6.2969440432624877</v>
+      </c>
+      <c r="E67">
+        <v>15</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="3"/>
+        <v>1.3051261404939396E-6</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="3"/>
+        <v>1.0069608688354492E-2</v>
+      </c>
+      <c r="M67" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8400644432137461</v>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1825156476629806</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="0"/>
+        <v>6.2959929164817776</v>
+      </c>
+      <c r="E68">
+        <v>15</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="3"/>
+        <v>6.525630702469698E-7</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="3"/>
+        <v>5.0348043441772461E-3</v>
+      </c>
+      <c r="M68" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8399133860321595</v>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1826667048445672</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69">
+        <v>65</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="0"/>
+        <v>6.2955174069666588</v>
+      </c>
+      <c r="E69">
+        <v>15</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="3"/>
+        <v>3.262815351234849E-7</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="3"/>
+        <v>2.517402172088623E-3</v>
+      </c>
+      <c r="M69" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8398378574413661</v>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.1827422334353606</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>66</v>
+      </c>
+      <c r="D70">
+        <f t="shared" ref="D70:D133" si="4">EXP(2-1.2*(LN(E70)-LN(AVERAGE(E:E)))+0.02*I70+0.025*J70+0.03*K70)</f>
+        <v>41.050380011770109</v>
+      </c>
+      <c r="E70">
+        <v>15</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>75</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="3"/>
+        <v>1.6314076756174245E-7</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="3"/>
+        <v>1.2587010860443115E-3</v>
+      </c>
+      <c r="M70" s="2">
+        <f t="shared" ref="M70:M108" si="5">LN(D70)</f>
+        <v>3.714800093145969</v>
+      </c>
+      <c r="N70" s="3">
+        <f t="shared" ref="N70:N108" si="6">M70-AVERAGE($M$5:$M$108)</f>
+        <v>0.69222000226924241</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>67</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="4"/>
+        <v>104.82383832964877</v>
+      </c>
+      <c r="E71">
+        <v>15</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>75</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <f t="shared" ref="I71:K108" si="7">I70*0.5+F71</f>
+        <v>8.1570383780871225E-8</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>112.5</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="7"/>
+        <v>6.2935054302215576E-4</v>
+      </c>
+      <c r="M71" s="2">
+        <f t="shared" si="5"/>
+        <v>4.6522812109982707</v>
+      </c>
+      <c r="N71" s="3">
+        <f t="shared" si="6"/>
+        <v>1.6297011201215441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>68</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="4"/>
+        <v>167.50643524904891</v>
+      </c>
+      <c r="E72">
+        <v>15</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>75</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="7"/>
+        <v>4.0785191890435613E-8</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>131.25</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="7"/>
+        <v>3.1467527151107788E-4</v>
+      </c>
+      <c r="M72" s="2">
+        <f t="shared" si="5"/>
+        <v>5.1210217699244218</v>
+      </c>
+      <c r="N72" s="3">
+        <f t="shared" si="6"/>
+        <v>2.0984416790476952</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73">
+        <v>69</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="4"/>
+        <v>32.472450384921814</v>
+      </c>
+      <c r="E73">
+        <v>15</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="7"/>
+        <v>2.0392595945217806E-8</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>65.625</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="7"/>
+        <v>1.5733763575553894E-4</v>
+      </c>
+      <c r="M73" s="2">
+        <f t="shared" si="5"/>
+        <v>3.4803920493874969</v>
+      </c>
+      <c r="N73" s="3">
+        <f t="shared" si="6"/>
+        <v>0.45781195851077028</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>70</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="4"/>
+        <v>14.297392659229482</v>
+      </c>
+      <c r="E74">
+        <v>15</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="7"/>
+        <v>1.0196297972608903E-8</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>32.8125</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="7"/>
+        <v>7.866881787776947E-5</v>
+      </c>
+      <c r="M74" s="2">
+        <f t="shared" si="5"/>
+        <v>2.6600771891190349</v>
+      </c>
+      <c r="N74" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.36250290175769173</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75">
+        <v>71</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="4"/>
+        <v>61.862845113712041</v>
+      </c>
+      <c r="E75">
+        <v>15</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>75</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="7"/>
+        <v>5.0981489863044516E-9</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>91.40625</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="7"/>
+        <v>3.9334408938884735E-5</v>
+      </c>
+      <c r="M75" s="2">
+        <f t="shared" si="5"/>
+        <v>4.1249197589848041</v>
+      </c>
+      <c r="N75" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1023396681080775</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>72</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="4"/>
+        <v>128.68158812005018</v>
+      </c>
+      <c r="E76">
+        <v>15</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>75</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="7"/>
+        <v>2.5490744931522258E-9</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="7"/>
+        <v>120.703125</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="7"/>
+        <v>1.9667204469442368E-5</v>
+      </c>
+      <c r="M76" s="2">
+        <f t="shared" si="5"/>
+        <v>4.8573410439176881</v>
+      </c>
+      <c r="N76" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8347609530409614</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77">
+        <v>73</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="4"/>
+        <v>185.59218010028769</v>
+      </c>
+      <c r="E77">
+        <v>15</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>75</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="7"/>
+        <v>1.2745372465761129E-9</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="7"/>
+        <v>135.3515625</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="7"/>
+        <v>9.8336022347211838E-6</v>
+      </c>
+      <c r="M77" s="2">
+        <f t="shared" si="5"/>
+        <v>5.2235516863841305</v>
+      </c>
+      <c r="N77" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2009715955074038</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>74</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="4"/>
+        <v>34.180558161561571</v>
+      </c>
+      <c r="E78">
+        <v>15</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="7"/>
+        <v>6.3726862328805645E-10</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="7"/>
+        <v>67.67578125</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="7"/>
+        <v>4.9168011173605919E-6</v>
+      </c>
+      <c r="M78" s="2">
+        <f t="shared" si="5"/>
+        <v>3.5316570076173517</v>
+      </c>
+      <c r="N78" s="3">
+        <f t="shared" si="6"/>
+        <v>0.50907691674062505</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79">
+        <v>75</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="4"/>
+        <v>14.668607532170288</v>
+      </c>
+      <c r="E79">
+        <v>15</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="7"/>
+        <v>3.1863431164402822E-10</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="7"/>
+        <v>33.837890625</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="7"/>
+        <v>2.4584005586802959E-6</v>
+      </c>
+      <c r="M79" s="2">
+        <f t="shared" si="5"/>
+        <v>2.6857096682339625</v>
+      </c>
+      <c r="N79" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.33687042264276412</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>76</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="4"/>
+        <v>62.660796602785339</v>
+      </c>
+      <c r="E80">
+        <v>15</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>75</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="7"/>
+        <v>1.5931715582201411E-10</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="7"/>
+        <v>91.9189453125</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="7"/>
+        <v>1.229200279340148E-6</v>
+      </c>
+      <c r="M80" s="2">
+        <f t="shared" si="5"/>
+        <v>4.1377359985422668</v>
+      </c>
+      <c r="N80" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1151559076655402</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>77</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="4"/>
+        <v>129.50884289301334</v>
+      </c>
+      <c r="E81">
+        <v>15</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>75</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="7"/>
+        <v>7.9658577911007056E-11</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="7"/>
+        <v>120.95947265625</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="7"/>
+        <v>6.1460013967007399E-7</v>
+      </c>
+      <c r="M81" s="2">
+        <f t="shared" si="5"/>
+        <v>4.8637491636964194</v>
+      </c>
+      <c r="N81" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8411690728196928</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>78</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="4"/>
+        <v>186.18778222322564</v>
+      </c>
+      <c r="E82">
+        <v>15</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>75</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="7"/>
+        <v>3.9829288955503528E-11</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="7"/>
+        <v>135.479736328125</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="7"/>
+        <v>3.0730006983503699E-7</v>
+      </c>
+      <c r="M82" s="2">
+        <f t="shared" si="5"/>
+        <v>5.226755746273497</v>
+      </c>
+      <c r="N82" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2041756553967704</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83">
+        <v>79</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="4"/>
+        <v>34.235360324894906</v>
+      </c>
+      <c r="E83">
+        <v>15</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="7"/>
+        <v>1.9914644477751764E-11</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="7"/>
+        <v>67.7398681640625</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="7"/>
+        <v>1.536500349175185E-7</v>
+      </c>
+      <c r="M83" s="2">
+        <f t="shared" si="5"/>
+        <v>3.5332590375620345</v>
+      </c>
+      <c r="N83" s="3">
+        <f t="shared" si="6"/>
+        <v>0.51067894668530789</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>80</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="4"/>
+        <v>14.680362013556246</v>
+      </c>
+      <c r="E84">
+        <v>15</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="7"/>
+        <v>9.957322238875882E-12</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="7"/>
+        <v>33.86993408203125</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="7"/>
+        <v>7.6825017458759248E-8</v>
+      </c>
+      <c r="M84" s="2">
+        <f t="shared" si="5"/>
+        <v>2.6865106832063037</v>
+      </c>
+      <c r="N84" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.33606940767042293</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85">
+        <v>81</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="4"/>
+        <v>62.685897747176796</v>
+      </c>
+      <c r="E85">
+        <v>15</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>75</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="7"/>
+        <v>4.978661119437941E-12</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="7"/>
+        <v>91.934967041015625</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="7"/>
+        <v>3.8412508729379624E-8</v>
+      </c>
+      <c r="M85" s="2">
+        <f t="shared" si="5"/>
+        <v>4.1381365060284381</v>
+      </c>
+      <c r="N85" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1155564151517114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86">
+        <v>82</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="4"/>
+        <v>129.53478012049223</v>
+      </c>
+      <c r="E86">
+        <v>15</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>75</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="7"/>
+        <v>2.4893305597189705E-12</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="7"/>
+        <v>120.96748352050781</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="7"/>
+        <v>1.9206254364689812E-8</v>
+      </c>
+      <c r="M86" s="2">
+        <f t="shared" si="5"/>
+        <v>4.8639494174395059</v>
+      </c>
+      <c r="N86" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8413693265627793</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87">
+        <v>83</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="4"/>
+        <v>186.20642555671282</v>
+      </c>
+      <c r="E87">
+        <v>15</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>75</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="7"/>
+        <v>1.2446652798594852E-12</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="7"/>
+        <v>135.48374176025391</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="7"/>
+        <v>9.603127182344906E-9</v>
+      </c>
+      <c r="M87" s="2">
+        <f t="shared" si="5"/>
+        <v>5.2268558731450394</v>
+      </c>
+      <c r="N87" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2042757822683128</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88">
+        <v>84</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="4"/>
+        <v>34.237074307561222</v>
+      </c>
+      <c r="E88">
+        <v>15</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="7"/>
+        <v>6.2233263992974262E-13</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="7"/>
+        <v>67.741870880126953</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="7"/>
+        <v>4.801563591172453E-9</v>
+      </c>
+      <c r="M88" s="2">
+        <f t="shared" si="5"/>
+        <v>3.5333091009978062</v>
+      </c>
+      <c r="N88" s="3">
+        <f t="shared" si="6"/>
+        <v>0.51072901012107952</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>85</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="4"/>
+        <v>14.680729492835928</v>
+      </c>
+      <c r="E89">
+        <v>15</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="7"/>
+        <v>3.1116631996487131E-13</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="7"/>
+        <v>33.870935440063477</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="7"/>
+        <v>2.4007817955862265E-9</v>
+      </c>
+      <c r="M89" s="2">
+        <f t="shared" si="5"/>
+        <v>2.6865357149241893</v>
+      </c>
+      <c r="N89" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.33604437595253733</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90">
+        <v>86</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="4"/>
+        <v>62.686682319940509</v>
+      </c>
+      <c r="E90">
+        <v>15</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>75</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="7"/>
+        <v>1.5558315998243566E-13</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="7"/>
+        <v>91.935467720031738</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="7"/>
+        <v>1.2003908977931133E-9</v>
+      </c>
+      <c r="M90" s="2">
+        <f t="shared" si="5"/>
+        <v>4.1381490218873811</v>
+      </c>
+      <c r="N90" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1155689310106545</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91">
+        <v>87</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="4"/>
+        <v>129.53559074254662</v>
+      </c>
+      <c r="E91">
+        <v>15</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>75</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="7"/>
+        <v>7.7791579991217828E-14</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="7"/>
+        <v>120.96773386001587</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="7"/>
+        <v>6.0019544889655663E-10</v>
+      </c>
+      <c r="M91" s="2">
+        <f t="shared" si="5"/>
+        <v>4.8639556753689766</v>
+      </c>
+      <c r="N91" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8413755844922499</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92">
+        <v>88</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="4"/>
+        <v>186.20700819096339</v>
+      </c>
+      <c r="E92">
+        <v>15</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>75</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="7"/>
+        <v>3.8895789995608914E-14</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="7"/>
+        <v>135.48386693000793</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="7"/>
+        <v>3.0009772444827831E-10</v>
+      </c>
+      <c r="M92" s="2">
+        <f t="shared" si="5"/>
+        <v>5.2268590021097747</v>
+      </c>
+      <c r="N92" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2042789112330481</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93">
+        <v>89</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="4"/>
+        <v>34.237127870902178</v>
+      </c>
+      <c r="E93">
+        <v>15</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="7"/>
+        <v>1.9447894997804457E-14</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="7"/>
+        <v>67.741933465003967</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="7"/>
+        <v>1.5004886222413916E-10</v>
+      </c>
+      <c r="M93" s="2">
+        <f t="shared" si="5"/>
+        <v>3.5333106654801734</v>
+      </c>
+      <c r="N93" s="3">
+        <f t="shared" si="6"/>
+        <v>0.51073057460344673</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>90</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="4"/>
+        <v>19.188454283246404</v>
+      </c>
+      <c r="E94">
+        <v>12</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="7"/>
+        <v>9.7239474989022285E-15</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="7"/>
+        <v>33.870966732501984</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="7"/>
+        <v>7.5024431112069578E-11</v>
+      </c>
+      <c r="M94" s="2">
+        <f t="shared" si="5"/>
+        <v>2.9543087587424246</v>
+      </c>
+      <c r="N94" s="3">
+        <f t="shared" si="6"/>
+        <v>-6.8271332134302032E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95">
+        <v>91</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="4"/>
+        <v>81.934625114380125</v>
+      </c>
+      <c r="E95">
+        <v>12</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>75</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="7"/>
+        <v>4.8619737494511142E-15</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="7"/>
+        <v>91.935483366250992</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="7"/>
+        <v>3.7512215556034789E-11</v>
+      </c>
+      <c r="M95" s="2">
+        <f t="shared" si="5"/>
+        <v>4.4059216745850245</v>
+      </c>
+      <c r="N95" s="3">
+        <f t="shared" si="6"/>
+        <v>1.3833415837082979</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96">
+        <v>92</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="4"/>
+        <v>25.96444578844353</v>
+      </c>
+      <c r="E96">
+        <v>12</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="7"/>
+        <v>2.4309868747255571E-15</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="7"/>
+        <v>45.967741683125496</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="7"/>
+        <v>1.8756107778017395E-11</v>
+      </c>
+      <c r="M96" s="2">
+        <f t="shared" si="5"/>
+        <v>3.2567281325063244</v>
+      </c>
+      <c r="N96" s="3">
+        <f t="shared" si="6"/>
+        <v>0.23414804162959779</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97">
+        <v>93</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="4"/>
+        <v>14.6162125531363</v>
+      </c>
+      <c r="E97">
+        <v>12</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="7"/>
+        <v>1.2154934373627786E-15</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="7"/>
+        <v>22.983870841562748</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="7"/>
+        <v>9.3780538890086973E-12</v>
+      </c>
+      <c r="M97" s="2">
+        <f t="shared" si="5"/>
+        <v>2.6821313614669746</v>
+      </c>
+      <c r="N97" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.34044872940975202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98">
+        <v>94</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="4"/>
+        <v>10.96636625917135</v>
+      </c>
+      <c r="E98">
+        <v>12</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="7"/>
+        <v>6.0774671868138928E-16</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="7"/>
+        <v>11.491935420781374</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="7"/>
+        <v>4.6890269445043486E-12</v>
+      </c>
+      <c r="M98" s="2">
+        <f t="shared" si="5"/>
+        <v>2.3948329759472995</v>
+      </c>
+      <c r="N98" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.62774711492942714</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99">
+        <v>95</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="4"/>
+        <v>9.4989739089370087</v>
+      </c>
+      <c r="E99">
+        <v>12</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="7"/>
+        <v>3.0387335934069464E-16</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="7"/>
+        <v>5.745967710390687</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="7"/>
+        <v>2.3445134722521743E-12</v>
+      </c>
+      <c r="M99" s="2">
+        <f t="shared" si="5"/>
+        <v>2.2511837831874617</v>
+      </c>
+      <c r="N99" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.77139630768926493</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100">
+        <v>96</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="4"/>
+        <v>8.8406392449083118</v>
+      </c>
+      <c r="E100">
+        <v>12</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="7"/>
+        <v>1.5193667967034732E-16</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="7"/>
+        <v>2.8729838551953435</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="7"/>
+        <v>1.1722567361260872E-12</v>
+      </c>
+      <c r="M100" s="2">
+        <f t="shared" si="5"/>
+        <v>2.179359186807543</v>
+      </c>
+      <c r="N100" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.8432209040691836</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101">
+        <v>97</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="4"/>
+        <v>8.5287847928514768</v>
+      </c>
+      <c r="E101">
+        <v>12</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="7"/>
+        <v>7.596833983517366E-17</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="7"/>
+        <v>1.4364919275976717</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="7"/>
+        <v>5.8612836806304358E-13</v>
+      </c>
+      <c r="M101" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1434468886175839</v>
+      </c>
+      <c r="N101" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.87913320225914271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102">
+        <v>98</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="4"/>
+        <v>8.3770074082110302</v>
+      </c>
+      <c r="E102">
+        <v>12</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="7"/>
+        <v>3.798416991758683E-17</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="7"/>
+        <v>0.71824596379883587</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="7"/>
+        <v>2.9306418403152179E-13</v>
+      </c>
+      <c r="M102" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1254907395226041</v>
+      </c>
+      <c r="N102" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.89708935135412249</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103">
+        <v>99</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="4"/>
+        <v>8.3021346208795652</v>
+      </c>
+      <c r="E103">
+        <v>12</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="7"/>
+        <v>1.8992084958793415E-17</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="7"/>
+        <v>0.35912298189941794</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="7"/>
+        <v>1.465320920157609E-13</v>
+      </c>
+      <c r="M103" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1165126649751143</v>
+      </c>
+      <c r="N103" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.90606742590161238</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104">
+        <v>100</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="4"/>
+        <v>8.2649495541345264</v>
+      </c>
+      <c r="E104">
+        <v>12</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="7"/>
+        <v>9.4960424793967075E-18</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="7"/>
+        <v>0.17956149094970897</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="7"/>
+        <v>7.3266046007880448E-14</v>
+      </c>
+      <c r="M104" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1120236277013693</v>
+      </c>
+      <c r="N104" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.91055646317535732</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105">
+        <v>101</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="4"/>
+        <v>8.2464195241056419</v>
+      </c>
+      <c r="E105">
+        <v>12</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="7"/>
+        <v>4.7480212396983538E-18</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="7"/>
+        <v>8.9780745474854484E-2</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="7"/>
+        <v>3.6633023003940224E-14</v>
+      </c>
+      <c r="M105" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1097791090644966</v>
+      </c>
+      <c r="N105" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.91280098181223002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106">
+        <v>102</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="4"/>
+        <v>8.2371700940512937</v>
+      </c>
+      <c r="E106">
+        <v>12</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="7"/>
+        <v>2.3740106198491769E-18</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="7"/>
+        <v>4.4890372737427242E-2</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="7"/>
+        <v>1.8316511501970112E-14</v>
+      </c>
+      <c r="M106" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1086568497460605</v>
+      </c>
+      <c r="N106" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.91392324113066614</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>6</v>
+      </c>
+      <c r="B107" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107">
+        <v>103</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="4"/>
+        <v>8.2325492701654106</v>
+      </c>
+      <c r="E107">
+        <v>12</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="7"/>
+        <v>1.1870053099245884E-18</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="7"/>
+        <v>2.2445186368713621E-2</v>
+      </c>
+      <c r="K107">
+        <f t="shared" si="7"/>
+        <v>9.158255750985056E-15</v>
+      </c>
+      <c r="M107" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1080957200868427</v>
+      </c>
+      <c r="N107" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.91448437078988398</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108">
+        <v>104</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="4"/>
+        <v>8.2302398303711168</v>
+      </c>
+      <c r="E108">
+        <v>12</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="7"/>
+        <v>5.9350265496229422E-19</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="7"/>
+        <v>1.1222593184356811E-2</v>
+      </c>
+      <c r="K108">
+        <f t="shared" si="7"/>
+        <v>4.579127875492528E-15</v>
+      </c>
+      <c r="M108" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1078151552572333</v>
+      </c>
+      <c r="N108" s="3">
+        <f t="shared" si="6"/>
+        <v>-0.91476493561949335</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E109">
+        <v>10</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <f>F109</f>
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <f>G109</f>
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <f>H109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E110">
+        <v>10</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <f>I109*0.5+F110</f>
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <f>J109*0.5+G110</f>
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <f>K109*0.5+H110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111">
+        <v>3</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E111">
+        <v>10</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <f t="shared" ref="I111:K174" si="8">I110*0.5+F111</f>
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E112">
+        <v>10</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113">
+        <v>5</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E113">
+        <v>10</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114">
+        <v>6</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E114">
+        <v>10</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115">
+        <v>7</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E115">
+        <v>10</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116">
+        <v>8</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E116">
+        <v>10</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117">
+        <v>9</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E117">
+        <v>10</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118">
+        <v>10</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E118">
+        <v>10</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119">
+        <v>11</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E119">
+        <v>10</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120">
+        <v>12</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E120">
+        <v>10</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121">
+        <v>13</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="4"/>
+        <v>10.240192912859774</v>
+      </c>
+      <c r="E121">
+        <v>10</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122">
+        <v>14</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="4"/>
+        <v>75.665359896992911</v>
+      </c>
+      <c r="E122">
+        <v>10</v>
+      </c>
+      <c r="F122">
+        <v>100</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123">
+        <v>15</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="4"/>
+        <v>205.67977285180959</v>
+      </c>
+      <c r="E123">
+        <v>10</v>
+      </c>
+      <c r="F123">
+        <v>100</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="J123">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124">
+        <v>16</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="4"/>
+        <v>339.10861645354925</v>
+      </c>
+      <c r="E124">
+        <v>10</v>
+      </c>
+      <c r="F124">
+        <v>100</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <f t="shared" si="8"/>
+        <v>175</v>
+      </c>
+      <c r="J124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125">
+        <v>17</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="4"/>
+        <v>58.928241539157753</v>
+      </c>
+      <c r="E125">
+        <v>10</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <f t="shared" si="8"/>
+        <v>87.5</v>
+      </c>
+      <c r="J125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126">
+        <v>18</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="4"/>
+        <v>24.564945784116286</v>
+      </c>
+      <c r="E126">
+        <v>10</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <f t="shared" si="8"/>
+        <v>43.75</v>
+      </c>
+      <c r="J126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127">
+        <v>19</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="4"/>
+        <v>15.860321047295738</v>
+      </c>
+      <c r="E127">
+        <v>10</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <f t="shared" si="8"/>
+        <v>21.875</v>
+      </c>
+      <c r="J127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128">
+        <v>20</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="4"/>
+        <v>12.744125987457851</v>
+      </c>
+      <c r="E128">
+        <v>10</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <f t="shared" si="8"/>
+        <v>10.9375</v>
+      </c>
+      <c r="J128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129">
+        <v>21</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="4"/>
+        <v>11.423760703785684</v>
+      </c>
+      <c r="E129">
+        <v>10</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <f t="shared" si="8"/>
+        <v>5.46875</v>
+      </c>
+      <c r="J129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130">
+        <v>22</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="4"/>
+        <v>10.815799249112946</v>
+      </c>
+      <c r="E130">
+        <v>10</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <f t="shared" si="8"/>
+        <v>2.734375</v>
+      </c>
+      <c r="J130">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131">
+        <v>23</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="4"/>
+        <v>10.524061517193847</v>
+      </c>
+      <c r="E131">
+        <v>10</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <f t="shared" si="8"/>
+        <v>1.3671875</v>
+      </c>
+      <c r="J131">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132">
+        <v>24</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="4"/>
+        <v>76.706951268364378</v>
+      </c>
+      <c r="E132">
+        <v>10</v>
+      </c>
+      <c r="F132">
+        <v>100</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <f t="shared" si="8"/>
+        <v>100.68359375</v>
+      </c>
+      <c r="J132">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133">
+        <v>25</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="4"/>
+        <v>207.09060360545556</v>
+      </c>
+      <c r="E133">
+        <v>10</v>
+      </c>
+      <c r="F133">
+        <v>100</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <f t="shared" si="8"/>
+        <v>150.341796875</v>
+      </c>
+      <c r="J133">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134">
+        <v>26</v>
+      </c>
+      <c r="D134">
+        <f t="shared" ref="D134:D197" si="9">EXP(2-1.2*(LN(E134)-LN(AVERAGE(E:E)))+0.02*I134+0.025*J134+0.03*K134)</f>
+        <v>340.26966218613165</v>
+      </c>
+      <c r="E134">
+        <v>10</v>
+      </c>
+      <c r="F134">
+        <v>100</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <f t="shared" si="8"/>
+        <v>175.1708984375</v>
+      </c>
+      <c r="J134">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135">
+        <v>27</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="9"/>
+        <v>59.029035085960992</v>
+      </c>
+      <c r="E135">
+        <v>10</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <f t="shared" si="8"/>
+        <v>87.58544921875</v>
+      </c>
+      <c r="J135">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136">
+        <v>28</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="9"/>
+        <v>24.585945309062431</v>
+      </c>
+      <c r="E136">
+        <v>10</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <f t="shared" si="8"/>
+        <v>43.792724609375</v>
+      </c>
+      <c r="J136">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137">
+        <v>29</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="9"/>
+        <v>15.867098755280347</v>
+      </c>
+      <c r="E137">
+        <v>10</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <f t="shared" si="8"/>
+        <v>21.8963623046875</v>
+      </c>
+      <c r="J137">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138">
+        <v>30</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="9"/>
+        <v>12.746848717289618</v>
+      </c>
+      <c r="E138">
+        <v>10</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <f t="shared" si="8"/>
+        <v>10.94818115234375</v>
+      </c>
+      <c r="J138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139">
+        <v>31</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="9"/>
+        <v>7.0233768867458046</v>
+      </c>
+      <c r="E139">
+        <v>15</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <f t="shared" si="8"/>
+        <v>5.474090576171875</v>
+      </c>
+      <c r="J139">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140">
+        <v>32</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="9"/>
+        <v>6.6492444695536337</v>
+      </c>
+      <c r="E140">
+        <v>15</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <f t="shared" si="8"/>
+        <v>2.7370452880859375</v>
+      </c>
+      <c r="J140">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141">
+        <v>33</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="9"/>
+        <v>6.4697196817971765</v>
+      </c>
+      <c r="E141">
+        <v>15</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <f t="shared" si="8"/>
+        <v>1.3685226440429688</v>
+      </c>
+      <c r="J141">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142">
+        <v>34</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="9"/>
+        <v>47.155354007831825</v>
+      </c>
+      <c r="E142">
+        <v>15</v>
+      </c>
+      <c r="F142">
+        <v>100</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <f t="shared" si="8"/>
+        <v>100.68426132202148</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143">
+        <v>35</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="9"/>
+        <v>127.30743918475332</v>
+      </c>
+      <c r="E143">
+        <v>15</v>
+      </c>
+      <c r="F143">
+        <v>100</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <f t="shared" si="8"/>
+        <v>150.34213066101074</v>
+      </c>
+      <c r="J143">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144">
+        <v>36</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="9"/>
+        <v>209.17759656375449</v>
+      </c>
+      <c r="E144">
+        <v>15</v>
+      </c>
+      <c r="F144">
+        <v>100</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <f t="shared" si="8"/>
+        <v>175.17106533050537</v>
+      </c>
+      <c r="J144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145">
+        <v>37</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="9"/>
+        <v>36.287487401159211</v>
+      </c>
+      <c r="E145">
+        <v>15</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <f t="shared" si="8"/>
+        <v>87.585532665252686</v>
+      </c>
+      <c r="J145">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146">
+        <v>38</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="9"/>
+        <v>15.113942399213457</v>
+      </c>
+      <c r="E146">
+        <v>15</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <f t="shared" si="8"/>
+        <v>43.792766332626343</v>
+      </c>
+      <c r="J146">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147">
+        <v>39</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="9"/>
+        <v>9.7541222660733613</v>
+      </c>
+      <c r="E147">
+        <v>15</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <f t="shared" si="8"/>
+        <v>21.896383166313171</v>
+      </c>
+      <c r="J147">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148">
+        <v>40</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="9"/>
+        <v>10.577468869422685</v>
+      </c>
+      <c r="E148">
+        <v>15</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>10</v>
+      </c>
+      <c r="I148">
+        <f t="shared" si="8"/>
+        <v>10.948191583156586</v>
+      </c>
+      <c r="J148">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149">
+        <v>41</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="9"/>
+        <v>11.014848703711642</v>
+      </c>
+      <c r="E149">
+        <v>15</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>10</v>
+      </c>
+      <c r="I149">
+        <f t="shared" si="8"/>
+        <v>5.4740957915782928</v>
+      </c>
+      <c r="J149">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150">
+        <v>42</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="9"/>
+        <v>11.240274734818675</v>
+      </c>
+      <c r="E150">
+        <v>15</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>10</v>
+      </c>
+      <c r="I150">
+        <f t="shared" si="8"/>
+        <v>2.7370478957891464</v>
+      </c>
+      <c r="J150">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <f t="shared" si="8"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151">
+        <v>43</v>
+      </c>
+      <c r="D151">
+        <f t="shared" si="9"/>
+        <v>11.354711952863022</v>
+      </c>
+      <c r="E151">
+        <v>15</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>10</v>
+      </c>
+      <c r="I151">
+        <f t="shared" si="8"/>
+        <v>1.3685239478945732</v>
+      </c>
+      <c r="J151">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <f t="shared" si="8"/>
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152">
+        <v>44</v>
+      </c>
+      <c r="D152">
+        <f t="shared" si="9"/>
+        <v>11.412366730264361</v>
+      </c>
+      <c r="E152">
+        <v>15</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>10</v>
+      </c>
+      <c r="I152">
+        <f t="shared" si="8"/>
+        <v>0.68426197394728661</v>
+      </c>
+      <c r="J152">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <f t="shared" si="8"/>
+        <v>19.375</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153">
+        <v>45</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="9"/>
+        <v>11.441303806874448</v>
+      </c>
+      <c r="E153">
+        <v>15</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>10</v>
+      </c>
+      <c r="I153">
+        <f t="shared" si="8"/>
+        <v>0.3421309869736433</v>
+      </c>
+      <c r="J153">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <f t="shared" si="8"/>
+        <v>19.6875</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154">
+        <v>46</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="9"/>
+        <v>11.455799848267615</v>
+      </c>
+      <c r="E154">
+        <v>15</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>10</v>
+      </c>
+      <c r="I154">
+        <f t="shared" si="8"/>
+        <v>0.17106549348682165</v>
+      </c>
+      <c r="J154">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <f t="shared" si="8"/>
+        <v>19.84375</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155">
+        <v>47</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="9"/>
+        <v>11.463054754899165</v>
+      </c>
+      <c r="E155">
+        <v>15</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>10</v>
+      </c>
+      <c r="I155">
+        <f t="shared" si="8"/>
+        <v>8.5532746743410826E-2</v>
+      </c>
+      <c r="J155">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="8"/>
+        <v>19.921875</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156">
+        <v>48</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="9"/>
+        <v>15.478404297910828</v>
+      </c>
+      <c r="E156">
+        <v>15</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>20</v>
+      </c>
+      <c r="I156">
+        <f t="shared" si="8"/>
+        <v>4.2766373371705413E-2</v>
+      </c>
+      <c r="J156">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="8"/>
+        <v>29.9609375</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157">
+        <v>49</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="9"/>
+        <v>13.324494792634002</v>
+      </c>
+      <c r="E157">
+        <v>15</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>10</v>
+      </c>
+      <c r="I157">
+        <f t="shared" si="8"/>
+        <v>2.1383186685852706E-2</v>
+      </c>
+      <c r="J157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <f t="shared" si="8"/>
+        <v>24.98046875</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158">
+        <v>50</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="9"/>
+        <v>12.362691558651548</v>
+      </c>
+      <c r="E158">
+        <v>15</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>10</v>
+      </c>
+      <c r="I158">
+        <f t="shared" si="8"/>
+        <v>1.0691593342926353E-2</v>
+      </c>
+      <c r="J158">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <f t="shared" si="8"/>
+        <v>22.490234375</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159">
+        <v>51</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="9"/>
+        <v>11.908146674781472</v>
+      </c>
+      <c r="E159">
+        <v>15</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>10</v>
+      </c>
+      <c r="I159">
+        <f t="shared" si="8"/>
+        <v>5.3457966714631766E-3</v>
+      </c>
+      <c r="J159">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <f t="shared" si="8"/>
+        <v>21.2451171875</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160">
+        <v>52</v>
+      </c>
+      <c r="D160">
+        <f t="shared" si="9"/>
+        <v>11.687180351421311</v>
+      </c>
+      <c r="E160">
+        <v>15</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>10</v>
+      </c>
+      <c r="I160">
+        <f t="shared" si="8"/>
+        <v>2.6728983357315883E-3</v>
+      </c>
+      <c r="J160">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <f t="shared" si="8"/>
+        <v>20.62255859375</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161">
+        <v>53</v>
+      </c>
+      <c r="D161">
+        <f t="shared" si="9"/>
+        <v>8.5773708323118285</v>
+      </c>
+      <c r="E161">
+        <v>15</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <f t="shared" si="8"/>
+        <v>1.3364491678657942E-3</v>
+      </c>
+      <c r="J161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <f t="shared" si="8"/>
+        <v>10.311279296875</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162">
+        <v>54</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="9"/>
+        <v>7.3481228260980114</v>
+      </c>
+      <c r="E162">
+        <v>15</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="8"/>
+        <v>6.6822458393289708E-4</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="8"/>
+        <v>5.1556396484375</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163">
+        <v>55</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="9"/>
+        <v>6.8012308681445051</v>
+      </c>
+      <c r="E163">
+        <v>15</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="8"/>
+        <v>3.3411229196644854E-4</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="8"/>
+        <v>2.57781982421875</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164">
+        <v>56</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="9"/>
+        <v>6.5432433481771399</v>
+      </c>
+      <c r="E164">
+        <v>15</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="8"/>
+        <v>1.6705614598322427E-4</v>
+      </c>
+      <c r="J164">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="8"/>
+        <v>1.288909912109375</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165">
+        <v>57</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="9"/>
+        <v>6.4179429147496352</v>
+      </c>
+      <c r="E165">
+        <v>15</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <f t="shared" si="8"/>
+        <v>8.3528072991612135E-5</v>
+      </c>
+      <c r="J165">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <f t="shared" si="8"/>
+        <v>0.6444549560546875</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166">
+        <v>58</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="9"/>
+        <v>6.3561953851569193</v>
+      </c>
+      <c r="E166">
+        <v>15</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <f t="shared" si="8"/>
+        <v>4.1764036495806067E-5</v>
+      </c>
+      <c r="J166">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <f t="shared" si="8"/>
+        <v>0.32222747802734375</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167">
+        <v>59</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="9"/>
+        <v>6.325544758060154</v>
+      </c>
+      <c r="E167">
+        <v>15</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <f t="shared" si="8"/>
+        <v>2.0882018247903034E-5</v>
+      </c>
+      <c r="J167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <f t="shared" si="8"/>
+        <v>0.16111373901367188</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168">
+        <v>60</v>
+      </c>
+      <c r="D168">
+        <f t="shared" si="9"/>
+        <v>6.3102749150385069</v>
+      </c>
+      <c r="E168">
+        <v>15</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <f t="shared" si="8"/>
+        <v>1.0441009123951517E-5</v>
+      </c>
+      <c r="J168">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <f t="shared" si="8"/>
+        <v>8.0556869506835938E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169">
+        <v>61</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="9"/>
+        <v>6.3026538220996295</v>
+      </c>
+      <c r="E169">
+        <v>15</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <f t="shared" si="8"/>
+        <v>5.2205045619757584E-6</v>
+      </c>
+      <c r="J169">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <f t="shared" si="8"/>
+        <v>4.0278434753417969E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170">
+        <v>62</v>
+      </c>
+      <c r="D170">
+        <f t="shared" si="9"/>
+        <v>6.2988467279017639</v>
+      </c>
+      <c r="E170">
+        <v>15</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <f t="shared" si="8"/>
+        <v>2.6102522809878792E-6</v>
+      </c>
+      <c r="J170">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <f t="shared" si="8"/>
+        <v>2.0139217376708984E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171">
+        <v>63</v>
+      </c>
+      <c r="D171">
+        <f t="shared" si="9"/>
+        <v>6.2969440432624877</v>
+      </c>
+      <c r="E171">
+        <v>15</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <f t="shared" si="8"/>
+        <v>1.3051261404939396E-6</v>
+      </c>
+      <c r="J171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <f t="shared" si="8"/>
+        <v>1.0069608688354492E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172">
+        <v>64</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="9"/>
+        <v>6.2959929164817776</v>
+      </c>
+      <c r="E172">
+        <v>15</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <f t="shared" si="8"/>
+        <v>6.525630702469698E-7</v>
+      </c>
+      <c r="J172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <f t="shared" si="8"/>
+        <v>5.0348043441772461E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173">
+        <v>65</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="9"/>
+        <v>6.2955174069666588</v>
+      </c>
+      <c r="E173">
+        <v>15</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <f t="shared" si="8"/>
+        <v>3.262815351234849E-7</v>
+      </c>
+      <c r="J173">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <f t="shared" si="8"/>
+        <v>2.517402172088623E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174">
+        <v>66</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="9"/>
+        <v>41.050380011770109</v>
+      </c>
+      <c r="E174">
+        <v>15</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>75</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <f t="shared" si="8"/>
+        <v>1.6314076756174245E-7</v>
+      </c>
+      <c r="J174">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="K174">
+        <f t="shared" si="8"/>
+        <v>1.2587010860443115E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175">
+        <v>67</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="9"/>
+        <v>104.82383832964877</v>
+      </c>
+      <c r="E175">
+        <v>15</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>75</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <f t="shared" ref="I175:K212" si="10">I174*0.5+F175</f>
+        <v>8.1570383780871225E-8</v>
+      </c>
+      <c r="J175">
+        <f t="shared" si="10"/>
+        <v>112.5</v>
+      </c>
+      <c r="K175">
+        <f t="shared" si="10"/>
+        <v>6.2935054302215576E-4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176">
+        <v>68</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="9"/>
+        <v>167.50643524904891</v>
+      </c>
+      <c r="E176">
+        <v>15</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>75</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <f t="shared" si="10"/>
+        <v>4.0785191890435613E-8</v>
+      </c>
+      <c r="J176">
+        <f t="shared" si="10"/>
+        <v>131.25</v>
+      </c>
+      <c r="K176">
+        <f t="shared" si="10"/>
+        <v>3.1467527151107788E-4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177">
+        <v>69</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="9"/>
+        <v>32.472450384921814</v>
+      </c>
+      <c r="E177">
+        <v>15</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <f t="shared" si="10"/>
+        <v>2.0392595945217806E-8</v>
+      </c>
+      <c r="J177">
+        <f t="shared" si="10"/>
+        <v>65.625</v>
+      </c>
+      <c r="K177">
+        <f t="shared" si="10"/>
+        <v>1.5733763575553894E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178">
+        <v>70</v>
+      </c>
+      <c r="D178">
+        <f t="shared" si="9"/>
+        <v>14.297392659229482</v>
+      </c>
+      <c r="E178">
+        <v>15</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <f t="shared" si="10"/>
+        <v>1.0196297972608903E-8</v>
+      </c>
+      <c r="J178">
+        <f t="shared" si="10"/>
+        <v>32.8125</v>
+      </c>
+      <c r="K178">
+        <f t="shared" si="10"/>
+        <v>7.866881787776947E-5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179">
+        <v>71</v>
+      </c>
+      <c r="D179">
+        <f t="shared" si="9"/>
+        <v>61.862845113712041</v>
+      </c>
+      <c r="E179">
+        <v>15</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+      <c r="G179">
+        <v>75</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <f t="shared" si="10"/>
+        <v>5.0981489863044516E-9</v>
+      </c>
+      <c r="J179">
+        <f t="shared" si="10"/>
+        <v>91.40625</v>
+      </c>
+      <c r="K179">
+        <f t="shared" si="10"/>
+        <v>3.9334408938884735E-5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180">
+        <v>72</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="9"/>
+        <v>128.68158812005018</v>
+      </c>
+      <c r="E180">
+        <v>15</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <v>75</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <f t="shared" si="10"/>
+        <v>2.5490744931522258E-9</v>
+      </c>
+      <c r="J180">
+        <f t="shared" si="10"/>
+        <v>120.703125</v>
+      </c>
+      <c r="K180">
+        <f t="shared" si="10"/>
+        <v>1.9667204469442368E-5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181">
+        <v>73</v>
+      </c>
+      <c r="D181">
+        <f t="shared" si="9"/>
+        <v>185.59218010028769</v>
+      </c>
+      <c r="E181">
+        <v>15</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>75</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <f t="shared" si="10"/>
+        <v>1.2745372465761129E-9</v>
+      </c>
+      <c r="J181">
+        <f t="shared" si="10"/>
+        <v>135.3515625</v>
+      </c>
+      <c r="K181">
+        <f t="shared" si="10"/>
+        <v>9.8336022347211838E-6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182">
+        <v>74</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="9"/>
+        <v>34.180558161561571</v>
+      </c>
+      <c r="E182">
+        <v>15</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <f t="shared" si="10"/>
+        <v>6.3726862328805645E-10</v>
+      </c>
+      <c r="J182">
+        <f t="shared" si="10"/>
+        <v>67.67578125</v>
+      </c>
+      <c r="K182">
+        <f t="shared" si="10"/>
+        <v>4.9168011173605919E-6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183">
+        <v>75</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="9"/>
+        <v>14.668607532170288</v>
+      </c>
+      <c r="E183">
+        <v>15</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <f t="shared" si="10"/>
+        <v>3.1863431164402822E-10</v>
+      </c>
+      <c r="J183">
+        <f t="shared" si="10"/>
+        <v>33.837890625</v>
+      </c>
+      <c r="K183">
+        <f t="shared" si="10"/>
+        <v>2.4584005586802959E-6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184">
+        <v>76</v>
+      </c>
+      <c r="D184">
+        <f t="shared" si="9"/>
+        <v>62.660796602785339</v>
+      </c>
+      <c r="E184">
+        <v>15</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>75</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <f t="shared" si="10"/>
+        <v>1.5931715582201411E-10</v>
+      </c>
+      <c r="J184">
+        <f t="shared" si="10"/>
+        <v>91.9189453125</v>
+      </c>
+      <c r="K184">
+        <f t="shared" si="10"/>
+        <v>1.229200279340148E-6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185">
+        <v>77</v>
+      </c>
+      <c r="D185">
+        <f t="shared" si="9"/>
+        <v>129.50884289301334</v>
+      </c>
+      <c r="E185">
+        <v>15</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>75</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <f t="shared" si="10"/>
+        <v>7.9658577911007056E-11</v>
+      </c>
+      <c r="J185">
+        <f t="shared" si="10"/>
+        <v>120.95947265625</v>
+      </c>
+      <c r="K185">
+        <f t="shared" si="10"/>
+        <v>6.1460013967007399E-7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186">
+        <v>78</v>
+      </c>
+      <c r="D186">
+        <f t="shared" si="9"/>
+        <v>186.18778222322564</v>
+      </c>
+      <c r="E186">
+        <v>15</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>75</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <f t="shared" si="10"/>
+        <v>3.9829288955503528E-11</v>
+      </c>
+      <c r="J186">
+        <f t="shared" si="10"/>
+        <v>135.479736328125</v>
+      </c>
+      <c r="K186">
+        <f t="shared" si="10"/>
+        <v>3.0730006983503699E-7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187">
+        <v>79</v>
+      </c>
+      <c r="D187">
+        <f t="shared" si="9"/>
+        <v>34.235360324894906</v>
+      </c>
+      <c r="E187">
+        <v>15</v>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <f t="shared" si="10"/>
+        <v>1.9914644477751764E-11</v>
+      </c>
+      <c r="J187">
+        <f t="shared" si="10"/>
+        <v>67.7398681640625</v>
+      </c>
+      <c r="K187">
+        <f t="shared" si="10"/>
+        <v>1.536500349175185E-7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188">
+        <v>80</v>
+      </c>
+      <c r="D188">
+        <f t="shared" si="9"/>
+        <v>14.680362013556246</v>
+      </c>
+      <c r="E188">
+        <v>15</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <f t="shared" si="10"/>
+        <v>9.957322238875882E-12</v>
+      </c>
+      <c r="J188">
+        <f t="shared" si="10"/>
+        <v>33.86993408203125</v>
+      </c>
+      <c r="K188">
+        <f t="shared" si="10"/>
+        <v>7.6825017458759248E-8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189">
+        <v>81</v>
+      </c>
+      <c r="D189">
+        <f t="shared" si="9"/>
+        <v>62.685897747176796</v>
+      </c>
+      <c r="E189">
+        <v>15</v>
+      </c>
+      <c r="F189">
+        <v>0</v>
+      </c>
+      <c r="G189">
+        <v>75</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <f t="shared" si="10"/>
+        <v>4.978661119437941E-12</v>
+      </c>
+      <c r="J189">
+        <f t="shared" si="10"/>
+        <v>91.934967041015625</v>
+      </c>
+      <c r="K189">
+        <f t="shared" si="10"/>
+        <v>3.8412508729379624E-8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190">
+        <v>82</v>
+      </c>
+      <c r="D190">
+        <f t="shared" si="9"/>
+        <v>129.53478012049223</v>
+      </c>
+      <c r="E190">
+        <v>15</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>75</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <f t="shared" si="10"/>
+        <v>2.4893305597189705E-12</v>
+      </c>
+      <c r="J190">
+        <f t="shared" si="10"/>
+        <v>120.96748352050781</v>
+      </c>
+      <c r="K190">
+        <f t="shared" si="10"/>
+        <v>1.9206254364689812E-8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191">
+        <v>83</v>
+      </c>
+      <c r="D191">
+        <f t="shared" si="9"/>
+        <v>186.20642555671282</v>
+      </c>
+      <c r="E191">
+        <v>15</v>
+      </c>
+      <c r="F191">
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <v>75</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <f t="shared" si="10"/>
+        <v>1.2446652798594852E-12</v>
+      </c>
+      <c r="J191">
+        <f t="shared" si="10"/>
+        <v>135.48374176025391</v>
+      </c>
+      <c r="K191">
+        <f t="shared" si="10"/>
+        <v>9.603127182344906E-9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192">
+        <v>84</v>
+      </c>
+      <c r="D192">
+        <f t="shared" si="9"/>
+        <v>34.237074307561222</v>
+      </c>
+      <c r="E192">
+        <v>15</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <f t="shared" si="10"/>
+        <v>6.2233263992974262E-13</v>
+      </c>
+      <c r="J192">
+        <f t="shared" si="10"/>
+        <v>67.741870880126953</v>
+      </c>
+      <c r="K192">
+        <f t="shared" si="10"/>
+        <v>4.801563591172453E-9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193">
+        <v>85</v>
+      </c>
+      <c r="D193">
+        <f t="shared" si="9"/>
+        <v>14.680729492835928</v>
+      </c>
+      <c r="E193">
+        <v>15</v>
+      </c>
+      <c r="F193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <f t="shared" si="10"/>
+        <v>3.1116631996487131E-13</v>
+      </c>
+      <c r="J193">
+        <f t="shared" si="10"/>
+        <v>33.870935440063477</v>
+      </c>
+      <c r="K193">
+        <f t="shared" si="10"/>
+        <v>2.4007817955862265E-9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A194" t="s">
+        <v>8</v>
+      </c>
+      <c r="B194" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194">
+        <v>86</v>
+      </c>
+      <c r="D194">
+        <f t="shared" si="9"/>
+        <v>62.686682319940509</v>
+      </c>
+      <c r="E194">
+        <v>15</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>75</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <f t="shared" si="10"/>
+        <v>1.5558315998243566E-13</v>
+      </c>
+      <c r="J194">
+        <f t="shared" si="10"/>
+        <v>91.935467720031738</v>
+      </c>
+      <c r="K194">
+        <f t="shared" si="10"/>
+        <v>1.2003908977931133E-9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A195" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195">
+        <v>87</v>
+      </c>
+      <c r="D195">
+        <f t="shared" si="9"/>
+        <v>129.53559074254662</v>
+      </c>
+      <c r="E195">
+        <v>15</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
+      </c>
+      <c r="G195">
+        <v>75</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <f t="shared" si="10"/>
+        <v>7.7791579991217828E-14</v>
+      </c>
+      <c r="J195">
+        <f t="shared" si="10"/>
+        <v>120.96773386001587</v>
+      </c>
+      <c r="K195">
+        <f t="shared" si="10"/>
+        <v>6.0019544889655663E-10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A196" t="s">
+        <v>8</v>
+      </c>
+      <c r="B196" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196">
+        <v>88</v>
+      </c>
+      <c r="D196">
+        <f t="shared" si="9"/>
+        <v>186.20700819096339</v>
+      </c>
+      <c r="E196">
+        <v>15</v>
+      </c>
+      <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>75</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <f t="shared" si="10"/>
+        <v>3.8895789995608914E-14</v>
+      </c>
+      <c r="J196">
+        <f t="shared" si="10"/>
+        <v>135.48386693000793</v>
+      </c>
+      <c r="K196">
+        <f t="shared" si="10"/>
+        <v>3.0009772444827831E-10</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A197" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197">
+        <v>89</v>
+      </c>
+      <c r="D197">
+        <f t="shared" si="9"/>
+        <v>34.237127870902178</v>
+      </c>
+      <c r="E197">
+        <v>15</v>
+      </c>
+      <c r="F197">
+        <v>0</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <f t="shared" si="10"/>
+        <v>1.9447894997804457E-14</v>
+      </c>
+      <c r="J197">
+        <f t="shared" si="10"/>
+        <v>67.741933465003967</v>
+      </c>
+      <c r="K197">
+        <f t="shared" si="10"/>
+        <v>1.5004886222413916E-10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A198" t="s">
+        <v>8</v>
+      </c>
+      <c r="B198" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198">
+        <v>90</v>
+      </c>
+      <c r="D198">
+        <f t="shared" ref="D198:D212" si="11">EXP(2-1.2*(LN(E198)-LN(AVERAGE(E:E)))+0.02*I198+0.025*J198+0.03*K198)</f>
+        <v>19.188454283246404</v>
+      </c>
+      <c r="E198">
+        <v>12</v>
+      </c>
+      <c r="F198">
+        <v>0</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <f t="shared" si="10"/>
+        <v>9.7239474989022285E-15</v>
+      </c>
+      <c r="J198">
+        <f t="shared" si="10"/>
+        <v>33.870966732501984</v>
+      </c>
+      <c r="K198">
+        <f t="shared" si="10"/>
+        <v>7.5024431112069578E-11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" t="s">
+        <v>8</v>
+      </c>
+      <c r="B199" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199">
+        <v>91</v>
+      </c>
+      <c r="D199">
+        <f t="shared" si="11"/>
+        <v>81.934625114380125</v>
+      </c>
+      <c r="E199">
+        <v>12</v>
+      </c>
+      <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>75</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <f t="shared" si="10"/>
+        <v>4.8619737494511142E-15</v>
+      </c>
+      <c r="J199">
+        <f t="shared" si="10"/>
+        <v>91.935483366250992</v>
+      </c>
+      <c r="K199">
+        <f t="shared" si="10"/>
+        <v>3.7512215556034789E-11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" t="s">
+        <v>8</v>
+      </c>
+      <c r="B200" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200">
+        <v>92</v>
+      </c>
+      <c r="D200">
+        <f t="shared" si="11"/>
+        <v>25.96444578844353</v>
+      </c>
+      <c r="E200">
+        <v>12</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <f t="shared" si="10"/>
+        <v>2.4309868747255571E-15</v>
+      </c>
+      <c r="J200">
+        <f t="shared" si="10"/>
+        <v>45.967741683125496</v>
+      </c>
+      <c r="K200">
+        <f t="shared" si="10"/>
+        <v>1.8756107778017395E-11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" t="s">
+        <v>8</v>
+      </c>
+      <c r="B201" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201">
+        <v>93</v>
+      </c>
+      <c r="D201">
+        <f t="shared" si="11"/>
+        <v>14.6162125531363</v>
+      </c>
+      <c r="E201">
+        <v>12</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <f t="shared" si="10"/>
+        <v>1.2154934373627786E-15</v>
+      </c>
+      <c r="J201">
+        <f t="shared" si="10"/>
+        <v>22.983870841562748</v>
+      </c>
+      <c r="K201">
+        <f t="shared" si="10"/>
+        <v>9.3780538890086973E-12</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202">
+        <v>94</v>
+      </c>
+      <c r="D202">
+        <f t="shared" si="11"/>
+        <v>10.96636625917135</v>
+      </c>
+      <c r="E202">
+        <v>12</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <f t="shared" si="10"/>
+        <v>6.0774671868138928E-16</v>
+      </c>
+      <c r="J202">
+        <f t="shared" si="10"/>
+        <v>11.491935420781374</v>
+      </c>
+      <c r="K202">
+        <f t="shared" si="10"/>
+        <v>4.6890269445043486E-12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" t="s">
+        <v>8</v>
+      </c>
+      <c r="B203" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203">
+        <v>95</v>
+      </c>
+      <c r="D203">
+        <f t="shared" si="11"/>
+        <v>9.4989739089370087</v>
+      </c>
+      <c r="E203">
+        <v>12</v>
+      </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <f t="shared" si="10"/>
+        <v>3.0387335934069464E-16</v>
+      </c>
+      <c r="J203">
+        <f t="shared" si="10"/>
+        <v>5.745967710390687</v>
+      </c>
+      <c r="K203">
+        <f t="shared" si="10"/>
+        <v>2.3445134722521743E-12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" t="s">
+        <v>8</v>
+      </c>
+      <c r="B204" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204">
+        <v>96</v>
+      </c>
+      <c r="D204">
+        <f t="shared" si="11"/>
+        <v>8.8406392449083118</v>
+      </c>
+      <c r="E204">
+        <v>12</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <f t="shared" si="10"/>
+        <v>1.5193667967034732E-16</v>
+      </c>
+      <c r="J204">
+        <f t="shared" si="10"/>
+        <v>2.8729838551953435</v>
+      </c>
+      <c r="K204">
+        <f t="shared" si="10"/>
+        <v>1.1722567361260872E-12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A205" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205">
+        <v>97</v>
+      </c>
+      <c r="D205">
+        <f t="shared" si="11"/>
+        <v>8.5287847928514768</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <f t="shared" si="10"/>
+        <v>7.596833983517366E-17</v>
+      </c>
+      <c r="J205">
+        <f t="shared" si="10"/>
+        <v>1.4364919275976717</v>
+      </c>
+      <c r="K205">
+        <f t="shared" si="10"/>
+        <v>5.8612836806304358E-13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A206" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206">
+        <v>98</v>
+      </c>
+      <c r="D206">
+        <f t="shared" si="11"/>
+        <v>8.3770074082110302</v>
+      </c>
+      <c r="E206">
+        <v>12</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <f t="shared" si="10"/>
+        <v>3.798416991758683E-17</v>
+      </c>
+      <c r="J206">
+        <f t="shared" si="10"/>
+        <v>0.71824596379883587</v>
+      </c>
+      <c r="K206">
+        <f t="shared" si="10"/>
+        <v>2.9306418403152179E-13</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207">
+        <v>99</v>
+      </c>
+      <c r="D207">
+        <f t="shared" si="11"/>
+        <v>8.3021346208795652</v>
+      </c>
+      <c r="E207">
+        <v>12</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <f t="shared" si="10"/>
+        <v>1.8992084958793415E-17</v>
+      </c>
+      <c r="J207">
+        <f t="shared" si="10"/>
+        <v>0.35912298189941794</v>
+      </c>
+      <c r="K207">
+        <f t="shared" si="10"/>
+        <v>1.465320920157609E-13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A208" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208" t="s">
+        <v>7</v>
+      </c>
+      <c r="C208">
+        <v>100</v>
+      </c>
+      <c r="D208">
+        <f t="shared" si="11"/>
+        <v>8.2649495541345264</v>
+      </c>
+      <c r="E208">
+        <v>12</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <f t="shared" si="10"/>
+        <v>9.4960424793967075E-18</v>
+      </c>
+      <c r="J208">
+        <f t="shared" si="10"/>
+        <v>0.17956149094970897</v>
+      </c>
+      <c r="K208">
+        <f t="shared" si="10"/>
+        <v>7.3266046007880448E-14</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A209" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209">
+        <v>101</v>
+      </c>
+      <c r="D209">
+        <f t="shared" si="11"/>
+        <v>8.2464195241056419</v>
+      </c>
+      <c r="E209">
+        <v>12</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <f t="shared" si="10"/>
+        <v>4.7480212396983538E-18</v>
+      </c>
+      <c r="J209">
+        <f t="shared" si="10"/>
+        <v>8.9780745474854484E-2</v>
+      </c>
+      <c r="K209">
+        <f t="shared" si="10"/>
+        <v>3.6633023003940224E-14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A210" t="s">
+        <v>8</v>
+      </c>
+      <c r="B210" t="s">
+        <v>7</v>
+      </c>
+      <c r="C210">
+        <v>102</v>
+      </c>
+      <c r="D210">
+        <f t="shared" si="11"/>
+        <v>8.2371700940512937</v>
+      </c>
+      <c r="E210">
+        <v>12</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <f t="shared" si="10"/>
+        <v>2.3740106198491769E-18</v>
+      </c>
+      <c r="J210">
+        <f t="shared" si="10"/>
+        <v>4.4890372737427242E-2</v>
+      </c>
+      <c r="K210">
+        <f t="shared" si="10"/>
+        <v>1.8316511501970112E-14</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A211" t="s">
+        <v>8</v>
+      </c>
+      <c r="B211" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211">
+        <v>103</v>
+      </c>
+      <c r="D211">
+        <f t="shared" si="11"/>
+        <v>8.2325492701654106</v>
+      </c>
+      <c r="E211">
+        <v>12</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <f t="shared" si="10"/>
+        <v>1.1870053099245884E-18</v>
+      </c>
+      <c r="J211">
+        <f t="shared" si="10"/>
+        <v>2.2445186368713621E-2</v>
+      </c>
+      <c r="K211">
+        <f t="shared" si="10"/>
+        <v>9.158255750985056E-15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A212" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212">
+        <v>104</v>
+      </c>
+      <c r="D212">
+        <f t="shared" si="11"/>
+        <v>8.2302398303711168</v>
+      </c>
+      <c r="E212">
+        <v>12</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <f t="shared" si="10"/>
+        <v>5.9350265496229422E-19</v>
+      </c>
+      <c r="J212">
+        <f t="shared" si="10"/>
+        <v>1.1222593184356811E-2</v>
+      </c>
+      <c r="K212">
+        <f t="shared" si="10"/>
+        <v>4.579127875492528E-15</v>
       </c>
     </row>
   </sheetData>
